--- a/data/Final_Blockers&Enablers_Explorer.xlsx
+++ b/data/Final_Blockers&Enablers_Explorer.xlsx
@@ -1,47 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" ns1:Ignorable="x15 xr xr6 xr10 xr2">
-  <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
-  <ns0:workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="https://uic.sharepoint.com/sites/PRJ-AIST_UIC/Documents partages/All you need to know on AIST is here/Blockers/Blockers &amp; Enablers Explorer/Version 2/"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="162" documentId="8_{61C54C15-BD8C-4007-AE0D-D71FF05DF67D}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{9029F2FF-C291-4D33-A715-A563D29E7146}"/>
-  <ns0:bookViews>
-    <ns0:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </ns0:bookViews>
-  <ns0:sheets>
-    <ns0:sheet name="Blockers" sheetId="1" ns7:id="rId1"/>
-    <ns0:sheet name="Blocker_Dependency_map" sheetId="7" ns7:id="rId2"/>
-    <ns0:sheet name="Enablers" sheetId="10" ns7:id="rId3"/>
-    <ns0:sheet name="Enablers_Dependency_Map" sheetId="11" ns7:id="rId4"/>
-    <ns0:sheet name="Readiness_Questions" sheetId="12" ns7:id="rId11"/>
-    <ns0:sheet name="Question_Blocker_Map" sheetId="13" ns7:id="rId12"/>
-  </ns0:sheets>
-  <ns0:definedNames>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blockers!$A$1:$L$42</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Enablers!$A$1:$H$1</ns0:definedName>
-  </ns0:definedNames>
-  <ns0:calcPr calcId="191028"/>
-  <ns0:extLst>
-    <ns0:ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <ns8:workbookPr chartTrackingRefBase="1"/>
-    </ns0:ext>
-    <ns0:ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <ns9:calcFeatures>
-        <ns9:feature name="microsoft.com:RD"/>
-        <ns9:feature name="microsoft.com:Single"/>
-        <ns9:feature name="microsoft.com:FV"/>
-        <ns9:feature name="microsoft.com:CNMTM"/>
-        <ns9:feature name="microsoft.com:LET_WF"/>
-        <ns9:feature name="microsoft.com:LAMBDA_WF"/>
-        <ns9:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </ns9:calcFeatures>
-    </ns0:ext>
-  </ns0:extLst>
-</ns0:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uic.sharepoint.com/sites/PRJ-AIST_UIC/Documents partages/All you need to know on AIST is here/Blockers/Blockers &amp; Enablers Explorer/Version 2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{61C54C15-BD8C-4007-AE0D-D71FF05DF67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9029F2FF-C291-4D33-A715-A563D29E7146}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Blockers" sheetId="1" r:id="rId1"/>
+    <sheet name="Blocker_Dependency_map" sheetId="7" r:id="rId2"/>
+    <sheet name="Enablers" sheetId="10" r:id="rId3"/>
+    <sheet name="Enablers_Dependency_Map" sheetId="11" r:id="rId4"/>
+    <sheet name="Readiness_Questions" sheetId="12" r:id="rId11"/>
+    <sheet name="Question_Blocker_Map" sheetId="13" r:id="rId12"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blockers!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Enablers!$A$1:$H$1</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3125,218 +3125,218 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:styleSheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
-  <ns0:fonts count="9">
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:color theme="1"/>
-      <ns0:name val="Aptos Narrow"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="11"/>
-      <ns0:color theme="0"/>
-      <ns0:name val="Aptos Narrow"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FF000000"/>
-      <ns0:name val="Aptos Narrow"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FFFFFFFF"/>
-      <ns0:name val="Aptos Narrow"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FF000000"/>
-      <ns0:name val="Arial"/>
-      <ns0:family val="2"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:name val="Carlito"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="10"/>
-      <ns0:name val="Arial"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="10"/>
-      <ns0:color rgb="FFFFFFFF"/>
-      <ns0:name val="Arial"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="14"/>
-      <ns0:name val="Arial"/>
-    </ns0:font>
-  </ns0:fonts>
-  <ns0:fills count="8">
-    <ns0:fill>
-      <ns0:patternFill patternType="none"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="gray125"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor theme="3" tint="9.9978637043366805E-2"/>
-        <ns0:bgColor indexed="65"/>
-      </ns0:patternFill>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor theme="3" tint="9.9978637043366805E-2"/>
-        <ns0:bgColor indexed="64"/>
-      </ns0:patternFill>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor rgb="FFC0E6F5"/>
-        <ns0:bgColor rgb="FFC0E6F5"/>
-      </ns0:patternFill>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="none"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="gray125"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor rgb="FF24476A"/>
-      </ns0:patternFill>
-    </ns0:fill>
-  </ns0:fills>
-  <ns0:borders count="3">
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right style="thin">
-        <ns0:color rgb="FF44B3E1"/>
-      </ns0:right>
-      <ns0:top style="thin">
-        <ns0:color rgb="FF44B3E1"/>
-      </ns0:top>
-      <ns0:bottom style="thin">
-        <ns0:color rgb="FF44B3E1"/>
-      </ns0:bottom>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-  </ns0:borders>
-  <ns0:cellStyleXfs count="2">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <ns0:xf numFmtId="0" fontId="5" fillId="5" borderId="2"/>
-  </ns0:cellStyleXfs>
-  <ns0:cellXfs count="22">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <ns0:alignment vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <ns0:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <ns0:alignment vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <ns0:alignment vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <ns0:alignment vertical="top"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <ns0:alignment vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <ns0:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1"/>
-    <ns0:xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <ns0:xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment vertical="top" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-  </ns0:cellXfs>
-  <ns0:cellStyles count="1">
-    <ns0:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </ns0:cellStyles>
-  <ns0:dxfs count="1">
-    <ns0:dxf>
-      <ns0:font>
-        <ns0:b/>
-        <ns0:i val="0"/>
-        <ns0:strike val="0"/>
-        <ns0:condense val="0"/>
-        <ns0:extend val="0"/>
-        <ns0:outline val="0"/>
-        <ns0:shadow val="0"/>
-        <ns0:u val="none"/>
-        <ns0:vertAlign val="baseline"/>
-        <ns0:sz val="11"/>
-        <ns0:color theme="0"/>
-        <ns0:name val="Aptos Narrow"/>
-        <ns0:scheme val="none"/>
-      </ns0:font>
-      <ns0:fill>
-        <ns0:patternFill patternType="solid">
-          <ns0:fgColor indexed="64"/>
-          <ns0:bgColor theme="3" tint="9.9978637043366805E-2"/>
-        </ns0:patternFill>
-      </ns0:fill>
-      <ns0:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </ns0:dxf>
-  </ns0:dxfs>
-  <ns0:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <ns0:extLst>
-    <ns0:ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns2:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ns0:ext>
-    <ns0:ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <ns3:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ns0:ext>
-  </ns0:extLst>
-</ns0:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
+  </fonts>
+  <fills count="8">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24476A"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2"/>
+  </cellStyleXfs>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3356,39 +3356,39 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:table xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReadinessQuestions" displayName="ReadinessQuestions" ref="A5:L31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <ns0:tableColumns count="12">
-    <ns0:tableColumn id="1" name="Question_ID"/>
-    <ns0:tableColumn id="2" name="Question"/>
-    <ns0:tableColumn id="3" name="Dimension"/>
-    <ns0:tableColumn id="4" name="Lifecycle_Stage"/>
-    <ns0:tableColumn id="5" name="Provisional_Stage_Gate"/>
-    <ns0:tableColumn id="6" name="Guidance"/>
-    <ns0:tableColumn id="7" name="Evidence_Examples"/>
-    <ns0:tableColumn id="8" name="Applicability"/>
-    <ns0:tableColumn id="9" name="Review_Status"/>
-    <ns0:tableColumn id="10" name="Review_Comments"/>
-    <ns0:tableColumn id="11" name="Source_Blocker_IDs"/>
-    <ns0:tableColumn id="12" name="Source_Stage_Gates"/>
-  </ns0:tableColumns>
-  <ns0:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</ns0:table>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReadinessQuestions" displayName="ReadinessQuestions" ref="A5:L31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="Question_ID"/>
+    <x:tableColumn id="2" name="Question"/>
+    <x:tableColumn id="3" name="Dimension"/>
+    <x:tableColumn id="4" name="Lifecycle_Stage"/>
+    <x:tableColumn id="5" name="Provisional_Stage_Gate"/>
+    <x:tableColumn id="6" name="Guidance"/>
+    <x:tableColumn id="7" name="Evidence_Examples"/>
+    <x:tableColumn id="8" name="Applicability"/>
+    <x:tableColumn id="9" name="Review_Status"/>
+    <x:tableColumn id="10" name="Review_Comments"/>
+    <x:tableColumn id="11" name="Source_Blocker_IDs"/>
+    <x:tableColumn id="12" name="Source_Stage_Gates"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:table xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="QuestionBlockerMap" displayName="QuestionBlockerMap" ref="A5:H50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <ns0:tableColumns count="8">
-    <ns0:tableColumn id="1" name="Question_ID"/>
-    <ns0:tableColumn id="2" name="Blocker_ID"/>
-    <ns0:tableColumn id="3" name="Blocker_Code"/>
-    <ns0:tableColumn id="4" name="Blocker_Title"/>
-    <ns0:tableColumn id="5" name="Relationship"/>
-    <ns0:tableColumn id="6" name="Rationale"/>
-    <ns0:tableColumn id="7" name="Review_Status"/>
-    <ns0:tableColumn id="8" name="Review_Comments"/>
-  </ns0:tableColumns>
-  <ns0:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</ns0:table>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="QuestionBlockerMap" displayName="QuestionBlockerMap" ref="A5:H50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="Question_ID"/>
+    <x:tableColumn id="2" name="Blocker_ID"/>
+    <x:tableColumn id="3" name="Blocker_Code"/>
+    <x:tableColumn id="4" name="Blocker_Title"/>
+    <x:tableColumn id="5" name="Relationship"/>
+    <x:tableColumn id="6" name="Rationale"/>
+    <x:tableColumn id="7" name="Review_Status"/>
+    <x:tableColumn id="8" name="Review_Comments"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5200,2314 +5200,2314 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheetFormatPr defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <ns0:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
-    <ns0:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <ns0:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
-    <ns0:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <ns0:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
-    <ns0:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
-    <ns0:col min="8" max="8" width="55" hidden="0" customWidth="1"/>
-    <ns0:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <ns0:col min="10" max="10" width="65" hidden="0" customWidth="1"/>
-    <ns0:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <ns0:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="21" t="str">
-        <ns0:v>Candidate AI project readiness questions</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="16" t="str">
-        <ns0:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="16" t="str">
-        <ns0:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" ht="32" customHeight="1">
-      <ns0:c r="A5" s="20" t="str">
-        <ns0:v>Question_ID</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" s="20" t="str">
-        <ns0:v>Question</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" s="20" t="str">
-        <ns0:v>Dimension</ns0:v>
-      </ns0:c>
-      <ns0:c r="D5" s="20" t="str">
-        <ns0:v>Lifecycle_Stage</ns0:v>
-      </ns0:c>
-      <ns0:c r="E5" s="20" t="str">
-        <ns0:v>Provisional_Stage_Gate</ns0:v>
-      </ns0:c>
-      <ns0:c r="F5" s="20" t="str">
-        <ns0:v>Guidance</ns0:v>
-      </ns0:c>
-      <ns0:c r="G5" s="20" t="str">
-        <ns0:v>Evidence_Examples</ns0:v>
-      </ns0:c>
-      <ns0:c r="H5" s="20" t="str">
-        <ns0:v>Applicability</ns0:v>
-      </ns0:c>
-      <ns0:c r="I5" s="20" t="str">
-        <ns0:v>Review_Status</ns0:v>
-      </ns0:c>
-      <ns0:c r="J5" s="20" t="str">
-        <ns0:v>Review_Comments</ns0:v>
-      </ns0:c>
-      <ns0:c r="K5" s="20" t="str">
-        <ns0:v>Source_Blocker_IDs</ns0:v>
-      </ns0:c>
-      <ns0:c r="L5" s="20" t="str">
-        <ns0:v>Source_Stage_Gates</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6" ht="85" customHeight="1">
-      <ns0:c r="A6" s="18" t="str">
-        <ns0:v>RQ-1114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B6" s="18" t="str">
-        <ns0:v>Is the project anchored in a validated operational problem, an accountable owner and the shared AI vision?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D6" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E6" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F6" s="18" t="str">
-        <ns0:v>Confirm problem evidence, ownership and strategic alignment separately. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G6" s="18" t="str">
-        <ns0:v>Problem baseline; owner approval; AI strategy alignment.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H6" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I6" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J6" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K6" s="18" t="str">
-        <ns0:v>1114; 1211</ns0:v>
-      </ns0:c>
-      <ns0:c r="L6" s="18" t="str">
-        <ns0:v>1114: Gate 0-Strategic Alignment &amp; Idea Validation; 1211: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7" ht="85" customHeight="1">
-      <ns0:c r="A7" s="18" t="str">
-        <ns0:v>RQ-1133-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="18" t="str">
-        <ns0:v>Is the expected value clear to each affected stakeholder group?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="18" t="str">
-        <ns0:v>Separate benefits for maintenance, asset management, operations and leadership. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G7" s="18" t="str">
-        <ns0:v>Stakeholder value statements; interviews; benefit measures.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I7" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J7" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K7" s="18" t="str">
-        <ns0:v>1133</ns0:v>
-      </ns0:c>
-      <ns0:c r="L7" s="18" t="str">
-        <ns0:v>1133: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8" ht="85" customHeight="1">
-      <ns0:c r="A8" s="18" t="str">
-        <ns0:v>RQ-1143-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" s="18" t="str">
-        <ns0:v>Does the business case address costs, benefits, risks and funding of shared foundations?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F8" s="18" t="str">
-        <ns0:v>Distinguish use-case costs from reusable platform, data and governance investments. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G8" s="18" t="str">
-        <ns0:v>Cost model; risk register; shared investment allocation.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H8" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I8" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J8" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K8" s="18" t="str">
-        <ns0:v>1143</ns0:v>
-      </ns0:c>
-      <ns0:c r="L8" s="18" t="str">
-        <ns0:v>1143: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9" ht="85" customHeight="1">
-      <ns0:c r="A9" s="18" t="str">
-        <ns0:v>RQ-1223-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" s="18" t="str">
-        <ns0:v>Have cross-functional priorities and competing AI initiatives been reconciled?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D9" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F9" s="18" t="str">
-        <ns0:v>Identify duplicated work and portfolio-level resource conflicts. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G9" s="18" t="str">
-        <ns0:v>Portfolio review; prioritisation decisions; resource commitments.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H9" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I9" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J9" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K9" s="18" t="str">
-        <ns0:v>1223</ns0:v>
-      </ns0:c>
-      <ns0:c r="L9" s="18" t="str">
-        <ns0:v>1223: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10" ht="85" customHeight="1">
-      <ns0:c r="A10" s="18" t="str">
-        <ns0:v>RQ-1233-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B10" s="18" t="str">
-        <ns0:v>Do teams share evidence-based readiness criteria, decision rights and a timely review process?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D10" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E10" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F10" s="18" t="str">
-        <ns0:v>Document readiness criteria, reviewers, approval authority and decision deadlines. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G10" s="18" t="str">
-        <ns0:v>Readiness checklist; governance charter; decision matrix; review calendar.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H10" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I10" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J10" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K10" s="18" t="str">
-        <ns0:v>1233; 1823</ns0:v>
-      </ns0:c>
-      <ns0:c r="L10" s="18" t="str">
-        <ns0:v>1233: Gate 0-Strategic Alignment &amp; Idea Validation; 1823: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11" ht="85" customHeight="1">
-      <ns0:c r="A11" s="18" t="str">
-        <ns0:v>RQ-1243-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B11" s="18" t="str">
-        <ns0:v>Is management sponsorship and funding sustained through deployment and operation?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D11" s="18" t="str">
-        <ns0:v>Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-      <ns0:c r="E11" s="18" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="F11" s="18" t="str">
-        <ns0:v>Confirm commitments beyond the pilot and arrangements for recurring reviews. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G11" s="18" t="str">
-        <ns0:v>Sponsor commitments; funding plan; steering review minutes.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H11" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I11" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J11" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K11" s="18" t="str">
-        <ns0:v>1243</ns0:v>
-      </ns0:c>
-      <ns0:c r="L11" s="18" t="str">
-        <ns0:v>1243: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12" ht="85" customHeight="1">
-      <ns0:c r="A12" s="18" t="str">
-        <ns0:v>RQ-1314-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B12" s="18" t="str">
-        <ns0:v>Are business ownership and human accountability defined for operational use beyond the prototype?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C12" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D12" s="18" t="str">
-        <ns0:v>Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-      <ns0:c r="E12" s="18" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="F12" s="18" t="str">
-        <ns0:v>Confirm benefit ownership and responsibilities for judgement, approval, action and escalation. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G12" s="18" t="str">
-        <ns0:v>Ownership agreement; decision workflow; responsibility matrix; escalation procedure.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H12" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I12" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J12" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K12" s="18" t="str">
-        <ns0:v>1314; 1323</ns0:v>
-      </ns0:c>
-      <ns0:c r="L12" s="18" t="str">
-        <ns0:v>1314: Gate 3- Operational Deployment &amp; Commissioning; 1323: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13" ht="85" customHeight="1">
-      <ns0:c r="A13" s="18" t="str">
-        <ns0:v>RQ-1334-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B13" s="18" t="str">
-        <ns0:v>Has the production operating model been funded and accepted through a reproducible deployment and support handover?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C13" s="18" t="str">
-        <ns0:v>Organisational; Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D13" s="18" t="str">
-        <ns0:v>Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-      <ns0:c r="E13" s="18" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="F13" s="18" t="str">
-        <ns0:v>Check support ownership, monitoring, incidents, deployment reproducibility and handover acceptance. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G13" s="18" t="str">
-        <ns0:v>Run budget; support acceptance; deployment records; telemetry and recovery tests.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H13" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I13" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J13" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K13" s="18" t="str">
-        <ns0:v>1334; 3413</ns0:v>
-      </ns0:c>
-      <ns0:c r="L13" s="18" t="str">
-        <ns0:v>1334: Gate 3- Operational Deployment &amp; Commissioning; 3413: Gate 4-Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14" ht="85" customHeight="1">
-      <ns0:c r="A14" s="18" t="str">
-        <ns0:v>RQ-1413-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B14" s="18" t="str">
-        <ns0:v>Do affected teams have the skills to interpret, challenge and use AI outputs?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C14" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D14" s="18" t="str">
-        <ns0:v>Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-      <ns0:c r="E14" s="18" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="F14" s="18" t="str">
-        <ns0:v>Assess role-specific competence and address training gaps. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G14" s="18" t="str">
-        <ns0:v>Skills assessment; training plan; competence demonstration.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H14" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I14" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J14" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K14" s="18" t="str">
-        <ns0:v>1413</ns0:v>
-      </ns0:c>
-      <ns0:c r="L14" s="18" t="str">
-        <ns0:v>1413: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15" ht="85" customHeight="1">
-      <ns0:c r="A15" s="18" t="str">
-        <ns0:v>RQ-1424-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B15" s="18" t="str">
-        <ns0:v>Have field users demonstrated that they can understand, challenge and use the AI outputs, with adoption concerns addressed?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C15" s="18" t="str">
-        <ns0:v>Organisational; Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D15" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E15" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F15" s="18" t="str">
-        <ns0:v>Assess interpretation and trust with affected users. Record unresolved concerns and workflow burden. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G15" s="18" t="str">
-        <ns0:v>User interpretation trials; explanation examples; co-design and adoption feedback.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H15" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I15" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J15" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K15" s="18" t="str">
-        <ns0:v>1424; 3523</ns0:v>
-      </ns0:c>
-      <ns0:c r="L15" s="18" t="str">
-        <ns0:v>1424: Gate 0-Strategic Alignment &amp; Idea Validation; 3523: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16" ht="85" customHeight="1">
-      <ns0:c r="A16" s="18" t="str">
-        <ns0:v>RQ-1433-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B16" s="18" t="str">
-        <ns0:v>Can the organisation absorb iterative releases and transition to changed AI capabilities?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C16" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D16" s="18" t="str">
-        <ns0:v>Retirement &amp; Transition</ns0:v>
-      </ns0:c>
-      <ns0:c r="E16" s="18" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="F16" s="18" t="str">
-        <ns0:v>Assess change capacity across releases and eventual replacement or retirement. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G16" s="18" t="str">
-        <ns0:v>Change capacity assessment; release plan; transition and training plan.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H16" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I16" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J16" s="18" t="str">
-        <ns0:v>Source assigns Gate 5. Review earlier lifecycle applicability. UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K16" s="18" t="str">
-        <ns0:v>1433</ns0:v>
-      </ns0:c>
-      <ns0:c r="L16" s="18" t="str">
-        <ns0:v>1433: Gate 5-Retirement &amp; Transition</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17" ht="85" customHeight="1">
-      <ns0:c r="A17" s="18" t="str">
-        <ns0:v>RQ-1511-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B17" s="18" t="str">
-        <ns0:v>Do decision-makers understand the proposed AI capability, data needs and limitations?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C17" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D17" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E17" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F17" s="18" t="str">
-        <ns0:v>Test expectations against realistic operational conditions and assurance needs. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G17" s="18" t="str">
-        <ns0:v>Capability briefing; limitations register; feasibility evidence.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H17" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I17" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J17" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K17" s="18" t="str">
-        <ns0:v>1511</ns0:v>
-      </ns0:c>
-      <ns0:c r="L17" s="18" t="str">
-        <ns0:v>1511: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18" ht="85" customHeight="1">
-      <ns0:c r="A18" s="18" t="str">
-        <ns0:v>RQ-1524-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B18" s="18" t="str">
-        <ns0:v>Does the proposed solution fit real railway field conditions and support needs?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C18" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D18" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E18" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F18" s="18" t="str">
-        <ns0:v>Consider possession windows, connectivity, shifts and maintenance practices. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G18" s="18" t="str">
-        <ns0:v>Field workflow observations; operational requirements; support assessment.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H18" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I18" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J18" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K18" s="18" t="str">
-        <ns0:v>1524</ns0:v>
-      </ns0:c>
-      <ns0:c r="L18" s="18" t="str">
-        <ns0:v>1524: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19" ht="85" customHeight="1">
-      <ns0:c r="A19" s="18" t="str">
-        <ns0:v>RQ-1614-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B19" s="18" t="str">
-        <ns0:v>Are cross-unit data ownership, access rules and sharing arrangements usable for reuse beyond the local pilot?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C19" s="18" t="str">
-        <ns0:v>Organisational; Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D19" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E19" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F19" s="18" t="str">
-        <ns0:v>Confirm governance and practical access across silos, including interoperability and control responsibilities. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G19" s="18" t="str">
-        <ns0:v>Data sharing agreements; access approvals; cross-unit reuse trial; governance decision records.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H19" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I19" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J19" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K19" s="18" t="str">
-        <ns0:v>1614; 3634</ns0:v>
-      </ns0:c>
-      <ns0:c r="L19" s="18" t="str">
-        <ns0:v>1614: Gate 0-Strategic Alignment &amp; Idea Validation; 3634: Gate 0-Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20" ht="85" customHeight="1">
-      <ns0:c r="A20" s="18" t="str">
-        <ns0:v>RQ-1713-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B20" s="18" t="str">
-        <ns0:v>Has a suitably informed legal team assessed applicable requirements and unresolved regulatory interpretations?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C20" s="18" t="str">
-        <ns0:v>Organisational</ns0:v>
-      </ns0:c>
-      <ns0:c r="D20" s="18" t="str">
-        <ns0:v>Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-      <ns0:c r="E20" s="18" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="F20" s="18" t="str">
-        <ns0:v>Confirm specialist capability, document interpretations and assign owners to unresolved questions. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G20" s="18" t="str">
-        <ns0:v>Legal assessment; specialist input; requirements register; unresolved issue log.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H20" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I20" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J20" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K20" s="18" t="str">
-        <ns0:v>1713; 1723</ns0:v>
-      </ns0:c>
-      <ns0:c r="L20" s="18" t="str">
-        <ns0:v>1713: Gate 1-Solution Architecture &amp; Feasibility; 1723: Gate 1-Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21" ht="85" customHeight="1">
-      <ns0:c r="A21" s="18" t="str">
-        <ns0:v>RQ-1811-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B21" s="18" t="str">
-        <ns0:v>Is the intended scale defined, and is model performance demonstrated across that scope and operational variation?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C21" s="18" t="str">
-        <ns0:v>Organisational; Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D21" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E21" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F21" s="18" t="str">
-        <ns0:v>Define sites, assets, users and workloads, then test false positives, missed detections and segment performance. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G21" s="18" t="str">
-        <ns0:v>Scaling scope; volume assumptions; segment validation results; acceptance thresholds.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H21" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I21" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J21" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K21" s="18" t="str">
-        <ns0:v>1811; 2513</ns0:v>
-      </ns0:c>
-      <ns0:c r="L21" s="18" t="str">
-        <ns0:v>1811: Gate 2- Solution Build &amp; Verification; 2513: Gate 4-Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22" ht="85" customHeight="1">
-      <ns0:c r="A22" s="18" t="str">
-        <ns0:v>RQ-1043-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B22" s="18" t="str">
-        <ns0:v>Is there a realistic incremental pathway from MVP and PoC to production, with owners and evidence at each milestone?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C22" s="18" t="str">
-        <ns0:v>Organisational; Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D22" s="18" t="str">
-        <ns0:v>Strategic Alignment &amp; Idea Validation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E22" s="18" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="F22" s="18" t="str">
-        <ns0:v>Assess increments, transition work, integration and assurance dependencies, resources and approval lead times. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G22" s="18" t="str">
-        <ns0:v>MVP roadmap; production transition plan; integrated schedule; field validation milestones.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H22" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I22" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J22" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K22" s="18" t="str">
-        <ns0:v>1043; 1833; 1921</ns0:v>
-      </ns0:c>
-      <ns0:c r="L22" s="18" t="str">
-        <ns0:v>1043: Gate 0-Strategic Alignment &amp; Idea Validation; 1833: Gate 0-Strategic Alignment &amp; Idea Validation; 1921: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23" ht="85" customHeight="1">
-      <ns0:c r="A23" s="18" t="str">
-        <ns0:v>RQ-2213-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B23" s="18" t="str">
-        <ns0:v>Can the governed platform and compute environment sustain the intended workload and operational constraints?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C23" s="18" t="str">
-        <ns0:v>Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D23" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E23" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F23" s="18" t="str">
-        <ns0:v>Check platform ownership, processing capacity, delivery channels, latency, connectivity and cloud or edge choices. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G23" s="18" t="str">
-        <ns0:v>Architecture review; platform ownership; load tests; compute sizing; connectivity assessment.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H23" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I23" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J23" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K23" s="18" t="str">
-        <ns0:v>2213; 2221</ns0:v>
-      </ns0:c>
-      <ns0:c r="L23" s="18" t="str">
-        <ns0:v>2213: Gate 4-Steady-State Operation &amp; Evolution; 2221: Gate 2- Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24" ht="85" customHeight="1">
-      <ns0:c r="A24" s="18" t="str">
-        <ns0:v>RQ-1024-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B24" s="18" t="str">
-        <ns0:v>Are data quality responsibilities and criteria agreed, and is quality and semantic consistency demonstrated across required systems?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C24" s="18" t="str">
-        <ns0:v>Organisational; Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D24" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E24" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F24" s="18" t="str">
-        <ns0:v>Check organisational ownership and technical profiling separately. Agree thresholds for this use case and common meaning across sources. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G24" s="18" t="str">
-        <ns0:v>Data quality policy; ownership matrix; data profiling; semantic dictionary; reconciliation tests.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H24" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I24" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J24" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K24" s="18" t="str">
-        <ns0:v>1024; 2123</ns0:v>
-      </ns0:c>
-      <ns0:c r="L24" s="18" t="str">
-        <ns0:v>1024: Gate 2- Solution Build &amp; Verification; 2123: Gate 2- Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25" ht="85" customHeight="1">
-      <ns0:c r="A25" s="18" t="str">
-        <ns0:v>RQ-3114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B25" s="18" t="str">
-        <ns0:v>Is the required data collected, retained and securely available through the target architecture at usable frequency and granularity?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C25" s="18" t="str">
-        <ns0:v>Cross-cutting; Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D25" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E25" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F25" s="18" t="str">
-        <ns0:v>Demonstrate coverage, retention, access, data movement and enforceable controls. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G25" s="18" t="str">
-        <ns0:v>Data inventory; retention plan; coverage tests; data flow diagram; access and control tests.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H25" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I25" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J25" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K25" s="18" t="str">
-        <ns0:v>3114; 2134</ns0:v>
-      </ns0:c>
-      <ns0:c r="L25" s="18" t="str">
-        <ns0:v>3114: Gate 2- Solution Build &amp; Verification; 2134: Gate 2- Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26" ht="85" customHeight="1">
-      <ns0:c r="A26" s="18" t="str">
-        <ns0:v>RQ-2231-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B26" s="18" t="str">
-        <ns0:v>Are software and vendor dependencies maintainable and sufficiently portable?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C26" s="18" t="str">
-        <ns0:v>Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D26" s="18" t="str">
-        <ns0:v>Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-      <ns0:c r="E26" s="18" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="F26" s="18" t="str">
-        <ns0:v>Assess specialist support, exit options and long-term sustainability. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G26" s="18" t="str">
-        <ns0:v>Dependency inventory; support terms; portability and exit assessment.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H26" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I26" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J26" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K26" s="18" t="str">
-        <ns0:v>2231</ns0:v>
-      </ns0:c>
-      <ns0:c r="L26" s="18" t="str">
-        <ns0:v>2231: Gate 4-Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27" ht="85" customHeight="1">
-      <ns0:c r="A27" s="18" t="str">
-        <ns0:v>RQ-2313-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B27" s="18" t="str">
-        <ns0:v>Can AI recommendations flow into enterprise and maintenance workflows, with users able to act and return field feedback?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C27" s="18" t="str">
-        <ns0:v>Technical; Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D27" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E27" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F27" s="18" t="str">
-        <ns0:v>Verify asset records, work orders, maintenance planning and feedback interfaces end to end. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G27" s="18" t="str">
-        <ns0:v>Interface specification; integration tests; work-order trial; operator feedback process.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H27" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I27" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J27" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K27" s="18" t="str">
-        <ns0:v>2313; 3333</ns0:v>
-      </ns0:c>
-      <ns0:c r="L27" s="18" t="str">
-        <ns0:v>2313: Gate 2- Solution Build &amp; Verification; 3333: Gate 3- Operational Deployment &amp; Commissioning</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28" ht="85" customHeight="1">
-      <ns0:c r="A28" s="18" t="str">
-        <ns0:v>RQ-2323-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B28" s="18" t="str">
-        <ns0:v>Are OT, monitoring, alarm procedures and operational workflows integrated reliably?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C28" s="18" t="str">
-        <ns0:v>Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D28" s="18" t="str">
-        <ns0:v>Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-      <ns0:c r="E28" s="18" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="F28" s="18" t="str">
-        <ns0:v>Test relevant live-system interfaces and failure handling. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G28" s="18" t="str">
-        <ns0:v>OT interface tests; alarm procedure; operational trial evidence.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H28" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I28" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J28" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K28" s="18" t="str">
-        <ns0:v>2323</ns0:v>
-      </ns0:c>
-      <ns0:c r="L28" s="18" t="str">
-        <ns0:v>2323: Gate 2- Solution Build &amp; Verification</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29" ht="85" customHeight="1">
-      <ns0:c r="A29" s="18" t="str">
-        <ns0:v>RQ-2423-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B29" s="18" t="str">
-        <ns0:v>Are model monitoring, retraining and controlled evolution arrangements in place?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C29" s="18" t="str">
-        <ns0:v>Technical</ns0:v>
-      </ns0:c>
-      <ns0:c r="D29" s="18" t="str">
-        <ns0:v>Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-      <ns0:c r="E29" s="18" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="F29" s="18" t="str">
-        <ns0:v>Define drift thresholds, response owners and revalidation triggers. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G29" s="18" t="str">
-        <ns0:v>Monitoring plan; drift tests; retraining and change control records.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H29" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I29" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J29" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K29" s="18" t="str">
-        <ns0:v>2423</ns0:v>
-      </ns0:c>
-      <ns0:c r="L29" s="18" t="str">
-        <ns0:v>2423: Gate 4-Steady-State Operation &amp; Evolution</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="30" ht="85" customHeight="1">
-      <ns0:c r="A30" s="18" t="str">
-        <ns0:v>RQ-3123-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B30" s="18" t="str">
-        <ns0:v>Have solution approaches been compared against operational and scalability requirements?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C30" s="18" t="str">
-        <ns0:v>Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D30" s="18" t="str">
-        <ns0:v>Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-      <ns0:c r="E30" s="18" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="F30" s="18" t="str">
-        <ns0:v>Include alternative technologies and justify the chosen approach. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G30" s="18" t="str">
-        <ns0:v>Options appraisal; architecture decision record; feasibility assessment.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H30" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I30" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J30" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K30" s="18" t="str">
-        <ns0:v>3123</ns0:v>
-      </ns0:c>
-      <ns0:c r="L30" s="18" t="str">
-        <ns0:v>3123: Gate 1-Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="31" ht="85" customHeight="1">
-      <ns0:c r="A31" s="18" t="str">
-        <ns0:v>RQ-3744-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B31" s="18" t="str">
-        <ns0:v>Have safety implications and oversight needs been identified, with an agreed assurance plan and evidence for reliability at scale?</ns0:v>
-      </ns0:c>
-      <ns0:c r="C31" s="18" t="str">
-        <ns0:v>Cross-cutting</ns0:v>
-      </ns0:c>
-      <ns0:c r="D31" s="18" t="str">
-        <ns0:v>Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-      <ns0:c r="E31" s="18" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="F31" s="18" t="str">
-        <ns0:v>Trace hazards and failure modes into human oversight and assurance evidence requirements. Confirm outstanding evidence with reviewers. Assess every component separately. Record partial readiness, gaps and evidence owners.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G31" s="18" t="str">
-        <ns0:v>Hazard analysis; oversight design; assurance plan; reliability tests; safety evidence register.</ns0:v>
-      </ns0:c>
-      <ns0:c r="H31" s="18" t="str">
-        <ns0:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</ns0:v>
-      </ns0:c>
-      <ns0:c r="I31" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="J31" s="18" t="str">
-        <ns0:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</ns0:v>
-      </ns0:c>
-      <ns0:c r="K31" s="18" t="str">
-        <ns0:v>3744; 3734</ns0:v>
-      </ns0:c>
-      <ns0:c r="L31" s="18" t="str">
-        <ns0:v>3744: Gate 1-Solution Architecture &amp; Feasibility; 3734: Gate 1-Solution Architecture &amp; Feasibility</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:dataValidations count="1">
-    <ns0:dataValidation type="list" sqref="I6:I31">
-      <ns0:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</ns0:formula1>
-    </ns0:dataValidation>
-  </ns0:dataValidations>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ns0:tableParts count="1">
-    <ns0:tablePart ns1:id="Rbe11539e17354f10"/>
-  </ns0:tableParts>
-</ns0:worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="55" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="65" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Candidate AI project readiness questions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="16" t="str">
+        <x:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>Question_ID</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>Question</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>Dimension</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>Lifecycle_Stage</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>Provisional_Stage_Gate</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>Guidance</x:v>
+      </x:c>
+      <x:c r="G5" s="20" t="str">
+        <x:v>Evidence_Examples</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="str">
+        <x:v>Applicability</x:v>
+      </x:c>
+      <x:c r="I5" s="20" t="str">
+        <x:v>Review_Status</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="str">
+        <x:v>Review_Comments</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="str">
+        <x:v>Source_Blocker_IDs</x:v>
+      </x:c>
+      <x:c r="L5" s="20" t="str">
+        <x:v>Source_Stage_Gates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="85" customHeight="1">
+      <x:c r="A6" s="18" t="str">
+        <x:v>RQ-1114-01</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="str">
+        <x:v>Is the project anchored in a validated operational problem, an accountable owner and the shared AI vision?</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="18" t="str">
+        <x:v>Confirm problem evidence, ownership and strategic alignment separately. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str">
+        <x:v>Problem baseline; owner approval; AI strategy alignment.</x:v>
+      </x:c>
+      <x:c r="H6" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I6" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K6" s="18" t="str">
+        <x:v>1114; 1211</x:v>
+      </x:c>
+      <x:c r="L6" s="18" t="str">
+        <x:v>1114: Gate 0-Strategic Alignment &amp; Idea Validation; 1211: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="85" customHeight="1">
+      <x:c r="A7" s="18" t="str">
+        <x:v>RQ-1133-01</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="str">
+        <x:v>Is the expected value clear to each affected stakeholder group?</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="str">
+        <x:v>Separate benefits for maintenance, asset management, operations and leadership. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G7" s="18" t="str">
+        <x:v>Stakeholder value statements; interviews; benefit measures.</x:v>
+      </x:c>
+      <x:c r="H7" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I7" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="str">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="L7" s="18" t="str">
+        <x:v>1133: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="85" customHeight="1">
+      <x:c r="A8" s="18" t="str">
+        <x:v>RQ-1143-01</x:v>
+      </x:c>
+      <x:c r="B8" s="18" t="str">
+        <x:v>Does the business case address costs, benefits, risks and funding of shared foundations?</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="18" t="str">
+        <x:v>Distinguish use-case costs from reusable platform, data and governance investments. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G8" s="18" t="str">
+        <x:v>Cost model; risk register; shared investment allocation.</x:v>
+      </x:c>
+      <x:c r="H8" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="str">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="L8" s="18" t="str">
+        <x:v>1143: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="85" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>RQ-1223-01</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>Have cross-functional priorities and competing AI initiatives been reconciled?</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="str">
+        <x:v>Identify duplicated work and portfolio-level resource conflicts. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="str">
+        <x:v>Portfolio review; prioritisation decisions; resource commitments.</x:v>
+      </x:c>
+      <x:c r="H9" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="str">
+        <x:v>1223</x:v>
+      </x:c>
+      <x:c r="L9" s="18" t="str">
+        <x:v>1223: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="85" customHeight="1">
+      <x:c r="A10" s="18" t="str">
+        <x:v>RQ-1233-01</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="str">
+        <x:v>Do teams share evidence-based readiness criteria, decision rights and a timely review process?</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="str">
+        <x:v>Document readiness criteria, reviewers, approval authority and decision deadlines. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="str">
+        <x:v>Readiness checklist; governance charter; decision matrix; review calendar.</x:v>
+      </x:c>
+      <x:c r="H10" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="str">
+        <x:v>1233; 1823</x:v>
+      </x:c>
+      <x:c r="L10" s="18" t="str">
+        <x:v>1233: Gate 0-Strategic Alignment &amp; Idea Validation; 1823: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="85" customHeight="1">
+      <x:c r="A11" s="18" t="str">
+        <x:v>RQ-1243-01</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="str">
+        <x:v>Is management sponsorship and funding sustained through deployment and operation?</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="str">
+        <x:v>Confirm commitments beyond the pilot and arrangements for recurring reviews. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="str">
+        <x:v>Sponsor commitments; funding plan; steering review minutes.</x:v>
+      </x:c>
+      <x:c r="H11" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I11" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="str">
+        <x:v>1243</x:v>
+      </x:c>
+      <x:c r="L11" s="18" t="str">
+        <x:v>1243: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="85" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>RQ-1314-01</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>Are business ownership and human accountability defined for operational use beyond the prototype?</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="str">
+        <x:v>Confirm benefit ownership and responsibilities for judgement, approval, action and escalation. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="str">
+        <x:v>Ownership agreement; decision workflow; responsibility matrix; escalation procedure.</x:v>
+      </x:c>
+      <x:c r="H12" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="str">
+        <x:v>1314; 1323</x:v>
+      </x:c>
+      <x:c r="L12" s="18" t="str">
+        <x:v>1314: Gate 3- Operational Deployment &amp; Commissioning; 1323: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="85" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>RQ-1334-01</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>Has the production operating model been funded and accepted through a reproducible deployment and support handover?</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>Organisational; Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>Check support ownership, monitoring, incidents, deployment reproducibility and handover acceptance. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="str">
+        <x:v>Run budget; support acceptance; deployment records; telemetry and recovery tests.</x:v>
+      </x:c>
+      <x:c r="H13" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I13" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="str">
+        <x:v>1334; 3413</x:v>
+      </x:c>
+      <x:c r="L13" s="18" t="str">
+        <x:v>1334: Gate 3- Operational Deployment &amp; Commissioning; 3413: Gate 4-Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="85" customHeight="1">
+      <x:c r="A14" s="18" t="str">
+        <x:v>RQ-1413-01</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="str">
+        <x:v>Do affected teams have the skills to interpret, challenge and use AI outputs?</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="str">
+        <x:v>Assess role-specific competence and address training gaps. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="str">
+        <x:v>Skills assessment; training plan; competence demonstration.</x:v>
+      </x:c>
+      <x:c r="H14" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I14" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="str">
+        <x:v>1413</x:v>
+      </x:c>
+      <x:c r="L14" s="18" t="str">
+        <x:v>1413: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="85" customHeight="1">
+      <x:c r="A15" s="18" t="str">
+        <x:v>RQ-1424-01</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="str">
+        <x:v>Have field users demonstrated that they can understand, challenge and use the AI outputs, with adoption concerns addressed?</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>Organisational; Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="str">
+        <x:v>Assess interpretation and trust with affected users. Record unresolved concerns and workflow burden. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="str">
+        <x:v>User interpretation trials; explanation examples; co-design and adoption feedback.</x:v>
+      </x:c>
+      <x:c r="H15" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="str">
+        <x:v>1424; 3523</x:v>
+      </x:c>
+      <x:c r="L15" s="18" t="str">
+        <x:v>1424: Gate 0-Strategic Alignment &amp; Idea Validation; 3523: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="85" customHeight="1">
+      <x:c r="A16" s="18" t="str">
+        <x:v>RQ-1433-01</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="str">
+        <x:v>Can the organisation absorb iterative releases and transition to changed AI capabilities?</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="str">
+        <x:v>Retirement &amp; Transition</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="str">
+        <x:v>Assess change capacity across releases and eventual replacement or retirement. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="str">
+        <x:v>Change capacity assessment; release plan; transition and training plan.</x:v>
+      </x:c>
+      <x:c r="H16" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="str">
+        <x:v>Source assigns Gate 5. Review earlier lifecycle applicability. UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="str">
+        <x:v>1433</x:v>
+      </x:c>
+      <x:c r="L16" s="18" t="str">
+        <x:v>1433: Gate 5-Retirement &amp; Transition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="85" customHeight="1">
+      <x:c r="A17" s="18" t="str">
+        <x:v>RQ-1511-01</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="str">
+        <x:v>Do decision-makers understand the proposed AI capability, data needs and limitations?</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="str">
+        <x:v>Test expectations against realistic operational conditions and assurance needs. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="str">
+        <x:v>Capability briefing; limitations register; feasibility evidence.</x:v>
+      </x:c>
+      <x:c r="H17" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="str">
+        <x:v>1511</x:v>
+      </x:c>
+      <x:c r="L17" s="18" t="str">
+        <x:v>1511: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="85" customHeight="1">
+      <x:c r="A18" s="18" t="str">
+        <x:v>RQ-1524-01</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="str">
+        <x:v>Does the proposed solution fit real railway field conditions and support needs?</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="str">
+        <x:v>Consider possession windows, connectivity, shifts and maintenance practices. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="str">
+        <x:v>Field workflow observations; operational requirements; support assessment.</x:v>
+      </x:c>
+      <x:c r="H18" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="str">
+        <x:v>1524</x:v>
+      </x:c>
+      <x:c r="L18" s="18" t="str">
+        <x:v>1524: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="85" customHeight="1">
+      <x:c r="A19" s="18" t="str">
+        <x:v>RQ-1614-01</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="str">
+        <x:v>Are cross-unit data ownership, access rules and sharing arrangements usable for reuse beyond the local pilot?</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>Organisational; Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="str">
+        <x:v>Confirm governance and practical access across silos, including interoperability and control responsibilities. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="str">
+        <x:v>Data sharing agreements; access approvals; cross-unit reuse trial; governance decision records.</x:v>
+      </x:c>
+      <x:c r="H19" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="str">
+        <x:v>1614; 3634</x:v>
+      </x:c>
+      <x:c r="L19" s="18" t="str">
+        <x:v>1614: Gate 0-Strategic Alignment &amp; Idea Validation; 3634: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="85" customHeight="1">
+      <x:c r="A20" s="18" t="str">
+        <x:v>RQ-1713-01</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="str">
+        <x:v>Has a suitably informed legal team assessed applicable requirements and unresolved regulatory interpretations?</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>Organisational</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="str">
+        <x:v>Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="str">
+        <x:v>Confirm specialist capability, document interpretations and assign owners to unresolved questions. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="str">
+        <x:v>Legal assessment; specialist input; requirements register; unresolved issue log.</x:v>
+      </x:c>
+      <x:c r="H20" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="str">
+        <x:v>1713; 1723</x:v>
+      </x:c>
+      <x:c r="L20" s="18" t="str">
+        <x:v>1713: Gate 1-Solution Architecture &amp; Feasibility; 1723: Gate 1-Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="85" customHeight="1">
+      <x:c r="A21" s="18" t="str">
+        <x:v>RQ-1811-01</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="str">
+        <x:v>Is the intended scale defined, and is model performance demonstrated across that scope and operational variation?</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>Organisational; Technical</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="str">
+        <x:v>Define sites, assets, users and workloads, then test false positives, missed detections and segment performance. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="str">
+        <x:v>Scaling scope; volume assumptions; segment validation results; acceptance thresholds.</x:v>
+      </x:c>
+      <x:c r="H21" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I21" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="str">
+        <x:v>1811; 2513</x:v>
+      </x:c>
+      <x:c r="L21" s="18" t="str">
+        <x:v>1811: Gate 2- Solution Build &amp; Verification; 2513: Gate 4-Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="85" customHeight="1">
+      <x:c r="A22" s="18" t="str">
+        <x:v>RQ-1043-01</x:v>
+      </x:c>
+      <x:c r="B22" s="18" t="str">
+        <x:v>Is there a realistic incremental pathway from MVP and PoC to production, with owners and evidence at each milestone?</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>Organisational; Technical</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>Assess increments, transition work, integration and assurance dependencies, resources and approval lead times. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="str">
+        <x:v>MVP roadmap; production transition plan; integrated schedule; field validation milestones.</x:v>
+      </x:c>
+      <x:c r="H22" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="str">
+        <x:v>1043; 1833; 1921</x:v>
+      </x:c>
+      <x:c r="L22" s="18" t="str">
+        <x:v>1043: Gate 0-Strategic Alignment &amp; Idea Validation; 1833: Gate 0-Strategic Alignment &amp; Idea Validation; 1921: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="85" customHeight="1">
+      <x:c r="A23" s="18" t="str">
+        <x:v>RQ-2213-01</x:v>
+      </x:c>
+      <x:c r="B23" s="18" t="str">
+        <x:v>Can the governed platform and compute environment sustain the intended workload and operational constraints?</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>Technical</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="str">
+        <x:v>Check platform ownership, processing capacity, delivery channels, latency, connectivity and cloud or edge choices. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="str">
+        <x:v>Architecture review; platform ownership; load tests; compute sizing; connectivity assessment.</x:v>
+      </x:c>
+      <x:c r="H23" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="str">
+        <x:v>2213; 2221</x:v>
+      </x:c>
+      <x:c r="L23" s="18" t="str">
+        <x:v>2213: Gate 4-Steady-State Operation &amp; Evolution; 2221: Gate 2- Solution Build &amp; Verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="85" customHeight="1">
+      <x:c r="A24" s="18" t="str">
+        <x:v>RQ-1024-01</x:v>
+      </x:c>
+      <x:c r="B24" s="18" t="str">
+        <x:v>Are data quality responsibilities and criteria agreed, and is quality and semantic consistency demonstrated across required systems?</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>Organisational; Technical</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="str">
+        <x:v>Check organisational ownership and technical profiling separately. Agree thresholds for this use case and common meaning across sources. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="str">
+        <x:v>Data quality policy; ownership matrix; data profiling; semantic dictionary; reconciliation tests.</x:v>
+      </x:c>
+      <x:c r="H24" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="str">
+        <x:v>1024; 2123</x:v>
+      </x:c>
+      <x:c r="L24" s="18" t="str">
+        <x:v>1024: Gate 2- Solution Build &amp; Verification; 2123: Gate 2- Solution Build &amp; Verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="85" customHeight="1">
+      <x:c r="A25" s="18" t="str">
+        <x:v>RQ-3114-01</x:v>
+      </x:c>
+      <x:c r="B25" s="18" t="str">
+        <x:v>Is the required data collected, retained and securely available through the target architecture at usable frequency and granularity?</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>Cross-cutting; Technical</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>Demonstrate coverage, retention, access, data movement and enforceable controls. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="str">
+        <x:v>Data inventory; retention plan; coverage tests; data flow diagram; access and control tests.</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I25" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="str">
+        <x:v>3114; 2134</x:v>
+      </x:c>
+      <x:c r="L25" s="18" t="str">
+        <x:v>3114: Gate 2- Solution Build &amp; Verification; 2134: Gate 2- Solution Build &amp; Verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="85" customHeight="1">
+      <x:c r="A26" s="18" t="str">
+        <x:v>RQ-2231-01</x:v>
+      </x:c>
+      <x:c r="B26" s="18" t="str">
+        <x:v>Are software and vendor dependencies maintainable and sufficiently portable?</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="str">
+        <x:v>Technical</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="str">
+        <x:v>Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F26" s="18" t="str">
+        <x:v>Assess specialist support, exit options and long-term sustainability. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G26" s="18" t="str">
+        <x:v>Dependency inventory; support terms; portability and exit assessment.</x:v>
+      </x:c>
+      <x:c r="H26" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I26" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="str">
+        <x:v>2231</x:v>
+      </x:c>
+      <x:c r="L26" s="18" t="str">
+        <x:v>2231: Gate 4-Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="85" customHeight="1">
+      <x:c r="A27" s="18" t="str">
+        <x:v>RQ-2313-01</x:v>
+      </x:c>
+      <x:c r="B27" s="18" t="str">
+        <x:v>Can AI recommendations flow into enterprise and maintenance workflows, with users able to act and return field feedback?</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>Technical; Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F27" s="18" t="str">
+        <x:v>Verify asset records, work orders, maintenance planning and feedback interfaces end to end. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G27" s="18" t="str">
+        <x:v>Interface specification; integration tests; work-order trial; operator feedback process.</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I27" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="str">
+        <x:v>2313; 3333</x:v>
+      </x:c>
+      <x:c r="L27" s="18" t="str">
+        <x:v>2313: Gate 2- Solution Build &amp; Verification; 3333: Gate 3- Operational Deployment &amp; Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="85" customHeight="1">
+      <x:c r="A28" s="18" t="str">
+        <x:v>RQ-2323-01</x:v>
+      </x:c>
+      <x:c r="B28" s="18" t="str">
+        <x:v>Are OT, monitoring, alarm procedures and operational workflows integrated reliably?</x:v>
+      </x:c>
+      <x:c r="C28" s="18" t="str">
+        <x:v>Technical</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="str">
+        <x:v>Solution Build &amp; Verification</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F28" s="18" t="str">
+        <x:v>Test relevant live-system interfaces and failure handling. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G28" s="18" t="str">
+        <x:v>OT interface tests; alarm procedure; operational trial evidence.</x:v>
+      </x:c>
+      <x:c r="H28" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I28" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="str">
+        <x:v>2323</x:v>
+      </x:c>
+      <x:c r="L28" s="18" t="str">
+        <x:v>2323: Gate 2- Solution Build &amp; Verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="85" customHeight="1">
+      <x:c r="A29" s="18" t="str">
+        <x:v>RQ-2423-01</x:v>
+      </x:c>
+      <x:c r="B29" s="18" t="str">
+        <x:v>Are model monitoring, retraining and controlled evolution arrangements in place?</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="str">
+        <x:v>Technical</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>Define drift thresholds, response owners and revalidation triggers. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>Monitoring plan; drift tests; retraining and change control records.</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I29" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="str">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="L29" s="18" t="str">
+        <x:v>2423: Gate 4-Steady-State Operation &amp; Evolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="85" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>RQ-3123-01</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="str">
+        <x:v>Have solution approaches been compared against operational and scalability requirements?</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="str">
+        <x:v>Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="18" t="str">
+        <x:v>Include alternative technologies and justify the chosen approach. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G30" s="18" t="str">
+        <x:v>Options appraisal; architecture decision record; feasibility assessment.</x:v>
+      </x:c>
+      <x:c r="H30" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I30" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="str">
+        <x:v>3123</x:v>
+      </x:c>
+      <x:c r="L30" s="18" t="str">
+        <x:v>3123: Gate 1-Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="85" customHeight="1">
+      <x:c r="A31" s="18" t="str">
+        <x:v>RQ-3744-01</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="str">
+        <x:v>Have safety implications and oversight needs been identified, with an agreed assurance plan and evidence for reliability at scale?</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="str">
+        <x:v>Cross-cutting</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="str">
+        <x:v>Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>Trace hazards and failure modes into human oversight and assurance evidence requirements. Confirm outstanding evidence with reviewers. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
+      </x:c>
+      <x:c r="G31" s="18" t="str">
+        <x:v>Hazard analysis; oversight design; assurance plan; reliability tests; safety evidence register.</x:v>
+      </x:c>
+      <x:c r="H31" s="18" t="str">
+        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
+      </x:c>
+      <x:c r="I31" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="str">
+        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="str">
+        <x:v>3744; 3734</x:v>
+      </x:c>
+      <x:c r="L31" s="18" t="str">
+        <x:v>3744: Gate 1-Solution Architecture &amp; Feasibility; 3734: Gate 1-Solution Architecture &amp; Feasibility</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I6:I31">
+      <x:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe11539e17354f10"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheetFormatPr defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <ns0:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <ns0:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <ns0:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
-    <ns0:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <ns0:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
-    <ns0:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <ns0:col min="8" max="8" width="65" hidden="0" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="21" t="str">
-        <ns0:v>Candidate question-to-blocker mappings</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="16" t="str">
-        <ns0:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="16" t="str">
-        <ns0:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" ht="32" customHeight="1">
-      <ns0:c r="A5" s="20" t="str">
-        <ns0:v>Question_ID</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" s="20" t="str">
-        <ns0:v>Blocker_ID</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" s="20" t="str">
-        <ns0:v>Blocker_Code</ns0:v>
-      </ns0:c>
-      <ns0:c r="D5" s="20" t="str">
-        <ns0:v>Blocker_Title</ns0:v>
-      </ns0:c>
-      <ns0:c r="E5" s="20" t="str">
-        <ns0:v>Relationship</ns0:v>
-      </ns0:c>
-      <ns0:c r="F5" s="20" t="str">
-        <ns0:v>Rationale</ns0:v>
-      </ns0:c>
-      <ns0:c r="G5" s="20" t="str">
-        <ns0:v>Review_Status</ns0:v>
-      </ns0:c>
-      <ns0:c r="H5" s="20" t="str">
-        <ns0:v>Review_Comments</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6" ht="65" customHeight="1">
-      <ns0:c r="A6" s="18" t="str">
-        <ns0:v>RQ-1114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B6" s="18" t="n">
-        <ns0:v>1114</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" s="18" t="str">
-        <ns0:v>B-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="D6" s="18" t="str">
-        <ns0:v>Technology-push AI initiatives without clear ownership</ns0:v>
-      </ns0:c>
-      <ns0:c r="E6" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F6" s="18" t="str">
-        <ns0:v>Question explicitly assesses Technology-push AI initiatives without clear ownership. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G6" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H6" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7" ht="65" customHeight="1">
-      <ns0:c r="A7" s="18" t="str">
-        <ns0:v>RQ-1114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="18" t="n">
-        <ns0:v>1211</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" s="18" t="str">
-        <ns0:v>B-04</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="18" t="str">
-        <ns0:v>Lack of shared AI vision</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="18" t="str">
-        <ns0:v>Question explicitly assesses Lack of shared AI vision. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G7" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8" ht="65" customHeight="1">
-      <ns0:c r="A8" s="18" t="str">
-        <ns0:v>RQ-1133-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" s="18" t="n">
-        <ns0:v>1133</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" s="18" t="str">
-        <ns0:v>B-02</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8" s="18" t="str">
-        <ns0:v>Unclear value articulation for stakeholder groups</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F8" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unclear value articulation for stakeholder groups. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G8" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H8" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9" ht="65" customHeight="1">
-      <ns0:c r="A9" s="18" t="str">
-        <ns0:v>RQ-1143-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" s="18" t="n">
-        <ns0:v>1143</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" s="18" t="str">
-        <ns0:v>B-03</ns0:v>
-      </ns0:c>
-      <ns0:c r="D9" s="18" t="str">
-        <ns0:v>Unclear financial implications, risks and investment logic</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F9" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unclear financial implications, risks and investment logic. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G9" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H9" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10" ht="65" customHeight="1">
-      <ns0:c r="A10" s="18" t="str">
-        <ns0:v>RQ-1223-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B10" s="18" t="n">
-        <ns0:v>1223</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" s="18" t="str">
-        <ns0:v>B-05</ns0:v>
-      </ns0:c>
-      <ns0:c r="D10" s="18" t="str">
-        <ns0:v>Fragmented AI priorities across silos</ns0:v>
-      </ns0:c>
-      <ns0:c r="E10" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F10" s="18" t="str">
-        <ns0:v>Question explicitly assesses Fragmented AI priorities across silos. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G10" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H10" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11" ht="65" customHeight="1">
-      <ns0:c r="A11" s="18" t="str">
-        <ns0:v>RQ-1233-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B11" s="18" t="n">
-        <ns0:v>1233</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" s="18" t="str">
-        <ns0:v>B-06</ns0:v>
-      </ns0:c>
-      <ns0:c r="D11" s="18" t="str">
-        <ns0:v>Slow or unclear AI governance</ns0:v>
-      </ns0:c>
-      <ns0:c r="E11" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F11" s="18" t="str">
-        <ns0:v>Question explicitly assesses Slow or unclear AI governance. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G11" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H11" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12" ht="65" customHeight="1">
-      <ns0:c r="A12" s="18" t="str">
-        <ns0:v>RQ-1233-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B12" s="18" t="n">
-        <ns0:v>1823</ns0:v>
-      </ns0:c>
-      <ns0:c r="C12" s="18" t="str">
-        <ns0:v>B-23</ns0:v>
-      </ns0:c>
-      <ns0:c r="D12" s="18" t="str">
-        <ns0:v>There is no shared understanding of AI project maturity and readiness across teams and decision-makers.</ns0:v>
-      </ns0:c>
-      <ns0:c r="E12" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F12" s="18" t="str">
-        <ns0:v>Question explicitly assesses There is no shared understanding of AI project maturity and readiness across teams and decision-makers.. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G12" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H12" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13" ht="65" customHeight="1">
-      <ns0:c r="A13" s="18" t="str">
-        <ns0:v>RQ-1243-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B13" s="18" t="n">
-        <ns0:v>1243</ns0:v>
-      </ns0:c>
-      <ns0:c r="C13" s="18" t="str">
-        <ns0:v>B-07</ns0:v>
-      </ns0:c>
-      <ns0:c r="D13" s="18" t="str">
-        <ns0:v>Insufficient sustained management commitment 'towards the end goal'</ns0:v>
-      </ns0:c>
-      <ns0:c r="E13" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F13" s="18" t="str">
-        <ns0:v>Question explicitly assesses Insufficient sustained management commitment 'towards the end goal'. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G13" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H13" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14" ht="65" customHeight="1">
-      <ns0:c r="A14" s="18" t="str">
-        <ns0:v>RQ-1314-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B14" s="18" t="n">
-        <ns0:v>1314</ns0:v>
-      </ns0:c>
-      <ns0:c r="C14" s="18" t="str">
-        <ns0:v>B-08</ns0:v>
-      </ns0:c>
-      <ns0:c r="D14" s="18" t="str">
-        <ns0:v>No business ownership beyond prototype</ns0:v>
-      </ns0:c>
-      <ns0:c r="E14" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F14" s="18" t="str">
-        <ns0:v>Question explicitly assesses No business ownership beyond prototype. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G14" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H14" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15" ht="65" customHeight="1">
-      <ns0:c r="A15" s="18" t="str">
-        <ns0:v>RQ-1314-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B15" s="18" t="n">
-        <ns0:v>1323</ns0:v>
-      </ns0:c>
-      <ns0:c r="C15" s="18" t="str">
-        <ns0:v>B-09</ns0:v>
-      </ns0:c>
-      <ns0:c r="D15" s="18" t="str">
-        <ns0:v>Unclear human accountability in AI-supported operational decisions</ns0:v>
-      </ns0:c>
-      <ns0:c r="E15" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F15" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unclear human accountability in AI-supported operational decisions. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G15" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H15" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16" ht="65" customHeight="1">
-      <ns0:c r="A16" s="18" t="str">
-        <ns0:v>RQ-1334-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B16" s="18" t="n">
-        <ns0:v>1334</ns0:v>
-      </ns0:c>
-      <ns0:c r="C16" s="18" t="str">
-        <ns0:v>B-10</ns0:v>
-      </ns0:c>
-      <ns0:c r="D16" s="18" t="str">
-        <ns0:v>No defined run model after go-live</ns0:v>
-      </ns0:c>
-      <ns0:c r="E16" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F16" s="18" t="str">
-        <ns0:v>Question explicitly assesses No defined run model after go-live. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G16" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H16" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17" ht="65" customHeight="1">
-      <ns0:c r="A17" s="18" t="str">
-        <ns0:v>RQ-1334-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B17" s="18" t="n">
-        <ns0:v>3413</ns0:v>
-      </ns0:c>
-      <ns0:c r="C17" s="18" t="str">
-        <ns0:v>B-34</ns0:v>
-      </ns0:c>
-      <ns0:c r="D17" s="18" t="str">
-        <ns0:v>Production-grade AI operations and handover gap</ns0:v>
-      </ns0:c>
-      <ns0:c r="E17" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F17" s="18" t="str">
-        <ns0:v>Question explicitly assesses Production-grade AI operations and handover gap. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G17" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H17" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18" ht="65" customHeight="1">
-      <ns0:c r="A18" s="18" t="str">
-        <ns0:v>RQ-1413-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B18" s="18" t="n">
-        <ns0:v>1413</ns0:v>
-      </ns0:c>
-      <ns0:c r="C18" s="18" t="str">
-        <ns0:v>B-11</ns0:v>
-      </ns0:c>
-      <ns0:c r="D18" s="18" t="str">
-        <ns0:v>Insufficient AI and digital skills across the organisation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E18" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F18" s="18" t="str">
-        <ns0:v>Question explicitly assesses Insufficient AI and digital skills across the organisation. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G18" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H18" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19" ht="65" customHeight="1">
-      <ns0:c r="A19" s="18" t="str">
-        <ns0:v>RQ-1424-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B19" s="18" t="n">
-        <ns0:v>1424</ns0:v>
-      </ns0:c>
-      <ns0:c r="C19" s="18" t="str">
-        <ns0:v>B-12</ns0:v>
-      </ns0:c>
-      <ns0:c r="D19" s="18" t="str">
-        <ns0:v>Low trust and cultural resistance to AI</ns0:v>
-      </ns0:c>
-      <ns0:c r="E19" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F19" s="18" t="str">
-        <ns0:v>Question explicitly assesses Low trust and cultural resistance to AI. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G19" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H19" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20" ht="65" customHeight="1">
-      <ns0:c r="A20" s="18" t="str">
-        <ns0:v>RQ-1424-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B20" s="18" t="n">
-        <ns0:v>3523</ns0:v>
-      </ns0:c>
-      <ns0:c r="C20" s="18" t="str">
-        <ns0:v>B-37</ns0:v>
-      </ns0:c>
-      <ns0:c r="D20" s="18" t="str">
-        <ns0:v>Limited explainability, interpretability and field trust</ns0:v>
-      </ns0:c>
-      <ns0:c r="E20" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F20" s="18" t="str">
-        <ns0:v>Question explicitly assesses Limited explainability, interpretability and field trust. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G20" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H20" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21" ht="65" customHeight="1">
-      <ns0:c r="A21" s="18" t="str">
-        <ns0:v>RQ-1433-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B21" s="18" t="n">
-        <ns0:v>1433</ns0:v>
-      </ns0:c>
-      <ns0:c r="C21" s="18" t="str">
-        <ns0:v>B-13</ns0:v>
-      </ns0:c>
-      <ns0:c r="D21" s="18" t="str">
-        <ns0:v>Limited capacity to absorb continuous change</ns0:v>
-      </ns0:c>
-      <ns0:c r="E21" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F21" s="18" t="str">
-        <ns0:v>Question explicitly assesses Limited capacity to absorb continuous change. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G21" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H21" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22" ht="65" customHeight="1">
-      <ns0:c r="A22" s="18" t="str">
-        <ns0:v>RQ-1511-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B22" s="18" t="n">
-        <ns0:v>1511</ns0:v>
-      </ns0:c>
-      <ns0:c r="C22" s="18" t="str">
-        <ns0:v>B-14</ns0:v>
-      </ns0:c>
-      <ns0:c r="D22" s="18" t="str">
-        <ns0:v>Unrealistic understanding of AI capabilities and limits among decision-makers</ns0:v>
-      </ns0:c>
-      <ns0:c r="E22" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F22" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unrealistic understanding of AI capabilities and limits among decision-makers. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G22" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H22" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23" ht="65" customHeight="1">
-      <ns0:c r="A23" s="18" t="str">
-        <ns0:v>RQ-1524-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B23" s="18" t="n">
-        <ns0:v>1524</ns0:v>
-      </ns0:c>
-      <ns0:c r="C23" s="18" t="str">
-        <ns0:v>B-15</ns0:v>
-      </ns0:c>
-      <ns0:c r="D23" s="18" t="str">
-        <ns0:v>Solutions misaligned with operational context</ns0:v>
-      </ns0:c>
-      <ns0:c r="E23" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F23" s="18" t="str">
-        <ns0:v>Question explicitly assesses Solutions misaligned with operational context. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G23" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H23" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24" ht="65" customHeight="1">
-      <ns0:c r="A24" s="18" t="str">
-        <ns0:v>RQ-1614-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B24" s="18" t="n">
-        <ns0:v>1614</ns0:v>
-      </ns0:c>
-      <ns0:c r="C24" s="18" t="str">
-        <ns0:v>B-16</ns0:v>
-      </ns0:c>
-      <ns0:c r="D24" s="18" t="str">
-        <ns0:v>Fragmented or restrictive data governance</ns0:v>
-      </ns0:c>
-      <ns0:c r="E24" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F24" s="18" t="str">
-        <ns0:v>Question explicitly assesses Fragmented or restrictive data governance. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G24" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H24" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25" ht="65" customHeight="1">
-      <ns0:c r="A25" s="18" t="str">
-        <ns0:v>RQ-1614-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B25" s="18" t="n">
-        <ns0:v>3634</ns0:v>
-      </ns0:c>
-      <ns0:c r="C25" s="18" t="str">
-        <ns0:v>B-18</ns0:v>
-      </ns0:c>
-      <ns0:c r="D25" s="18" t="str">
-        <ns0:v>Organisational data silos limiting reuse and scaling</ns0:v>
-      </ns0:c>
-      <ns0:c r="E25" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F25" s="18" t="str">
-        <ns0:v>Question explicitly assesses Organisational data silos limiting reuse and scaling. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G25" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H25" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26" ht="65" customHeight="1">
-      <ns0:c r="A26" s="18" t="str">
-        <ns0:v>RQ-1713-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B26" s="18" t="n">
-        <ns0:v>1713</ns0:v>
-      </ns0:c>
-      <ns0:c r="C26" s="18" t="str">
-        <ns0:v>B-19</ns0:v>
-      </ns0:c>
-      <ns0:c r="D26" s="18" t="str">
-        <ns0:v>Limited AI expertise in legal functions</ns0:v>
-      </ns0:c>
-      <ns0:c r="E26" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F26" s="18" t="str">
-        <ns0:v>Question explicitly assesses Limited AI expertise in legal functions. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G26" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H26" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27" ht="65" customHeight="1">
-      <ns0:c r="A27" s="18" t="str">
-        <ns0:v>RQ-1713-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B27" s="18" t="n">
-        <ns0:v>1723</ns0:v>
-      </ns0:c>
-      <ns0:c r="C27" s="18" t="str">
-        <ns0:v>B-20</ns0:v>
-      </ns0:c>
-      <ns0:c r="D27" s="18" t="str">
-        <ns0:v>Unclear regulatory interpretation increases perceived risk</ns0:v>
-      </ns0:c>
-      <ns0:c r="E27" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F27" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unclear regulatory interpretation increases perceived risk. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G27" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H27" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28" ht="65" customHeight="1">
-      <ns0:c r="A28" s="18" t="str">
-        <ns0:v>RQ-1811-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B28" s="18" t="n">
-        <ns0:v>1811</ns0:v>
-      </ns0:c>
-      <ns0:c r="C28" s="18" t="str">
-        <ns0:v>B-22</ns0:v>
-      </ns0:c>
-      <ns0:c r="D28" s="18" t="str">
-        <ns0:v>Ambiguous definition of scaling</ns0:v>
-      </ns0:c>
-      <ns0:c r="E28" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F28" s="18" t="str">
-        <ns0:v>Question explicitly assesses Ambiguous definition of scaling. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G28" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H28" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29" ht="65" customHeight="1">
-      <ns0:c r="A29" s="18" t="str">
-        <ns0:v>RQ-1811-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B29" s="18" t="n">
-        <ns0:v>2513</ns0:v>
-      </ns0:c>
-      <ns0:c r="C29" s="18" t="str">
-        <ns0:v>B-36</ns0:v>
-      </ns0:c>
-      <ns0:c r="D29" s="18" t="str">
-        <ns0:v>Model performance degrades with scale</ns0:v>
-      </ns0:c>
-      <ns0:c r="E29" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F29" s="18" t="str">
-        <ns0:v>Question explicitly assesses Model performance degrades with scale. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G29" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H29" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="30" ht="65" customHeight="1">
-      <ns0:c r="A30" s="18" t="str">
-        <ns0:v>RQ-1043-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B30" s="18" t="n">
-        <ns0:v>1043</ns0:v>
-      </ns0:c>
-      <ns0:c r="C30" s="18" t="str">
-        <ns0:v>B-40</ns0:v>
-      </ns0:c>
-      <ns0:c r="D30" s="18" t="str">
-        <ns0:v>Weak MVP and incremental delivery discipline</ns0:v>
-      </ns0:c>
-      <ns0:c r="E30" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F30" s="18" t="str">
-        <ns0:v>Question explicitly assesses Weak MVP and incremental delivery discipline. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G30" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H30" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="31" ht="65" customHeight="1">
-      <ns0:c r="A31" s="18" t="str">
-        <ns0:v>RQ-1043-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B31" s="18" t="n">
-        <ns0:v>1833</ns0:v>
-      </ns0:c>
-      <ns0:c r="C31" s="18" t="str">
-        <ns0:v>B-24</ns0:v>
-      </ns0:c>
-      <ns0:c r="D31" s="18" t="str">
-        <ns0:v>PoC to production transition stalls</ns0:v>
-      </ns0:c>
-      <ns0:c r="E31" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F31" s="18" t="str">
-        <ns0:v>Question explicitly assesses PoC to production transition stalls. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G31" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H31" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32" ht="65" customHeight="1">
-      <ns0:c r="A32" s="18" t="str">
-        <ns0:v>RQ-1043-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B32" s="18" t="n">
-        <ns0:v>1921</ns0:v>
-      </ns0:c>
-      <ns0:c r="C32" s="18" t="str">
-        <ns0:v>B-42</ns0:v>
-      </ns0:c>
-      <ns0:c r="D32" s="18" t="str">
-        <ns0:v>Unrealistic delivery timelines and scaling ambition</ns0:v>
-      </ns0:c>
-      <ns0:c r="E32" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F32" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unrealistic delivery timelines and scaling ambition. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G32" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H32" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33" ht="65" customHeight="1">
-      <ns0:c r="A33" s="18" t="str">
-        <ns0:v>RQ-2213-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B33" s="18" t="n">
-        <ns0:v>2213</ns0:v>
-      </ns0:c>
-      <ns0:c r="C33" s="18" t="str">
-        <ns0:v>B-28</ns0:v>
-      </ns0:c>
-      <ns0:c r="D33" s="18" t="str">
-        <ns0:v>Immature platform architecture and fragmented IT foundations</ns0:v>
-      </ns0:c>
-      <ns0:c r="E33" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F33" s="18" t="str">
-        <ns0:v>Question explicitly assesses Immature platform architecture and fragmented IT foundations. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G33" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H33" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34" ht="65" customHeight="1">
-      <ns0:c r="A34" s="18" t="str">
-        <ns0:v>RQ-2213-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B34" s="18" t="n">
-        <ns0:v>2221</ns0:v>
-      </ns0:c>
-      <ns0:c r="C34" s="18" t="str">
-        <ns0:v>B-29</ns0:v>
-      </ns0:c>
-      <ns0:c r="D34" s="18" t="str">
-        <ns0:v>Compute environment constraints for AI deployment</ns0:v>
-      </ns0:c>
-      <ns0:c r="E34" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F34" s="18" t="str">
-        <ns0:v>Question explicitly assesses Compute environment constraints for AI deployment. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G34" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H34" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35" ht="65" customHeight="1">
-      <ns0:c r="A35" s="18" t="str">
-        <ns0:v>RQ-1024-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B35" s="18" t="n">
-        <ns0:v>1024</ns0:v>
-      </ns0:c>
-      <ns0:c r="C35" s="18" t="str">
-        <ns0:v>B-39</ns0:v>
-      </ns0:c>
-      <ns0:c r="D35" s="18" t="str">
-        <ns0:v>Inconsistent data quality management across AI use cases</ns0:v>
-      </ns0:c>
-      <ns0:c r="E35" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F35" s="18" t="str">
-        <ns0:v>Question explicitly assesses Inconsistent data quality management across AI use cases. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G35" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H35" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36" ht="65" customHeight="1">
-      <ns0:c r="A36" s="18" t="str">
-        <ns0:v>RQ-1024-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B36" s="18" t="n">
-        <ns0:v>2123</ns0:v>
-      </ns0:c>
-      <ns0:c r="C36" s="18" t="str">
-        <ns0:v>B-26</ns0:v>
-      </ns0:c>
-      <ns0:c r="D36" s="18" t="str">
-        <ns0:v>Data quality, consistency and semantic structure</ns0:v>
-      </ns0:c>
-      <ns0:c r="E36" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F36" s="18" t="str">
-        <ns0:v>Question explicitly assesses Data quality, consistency and semantic structure. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G36" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H36" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="37" ht="65" customHeight="1">
-      <ns0:c r="A37" s="18" t="str">
-        <ns0:v>RQ-3114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B37" s="18" t="n">
-        <ns0:v>3114</ns0:v>
-      </ns0:c>
-      <ns0:c r="C37" s="18" t="str">
-        <ns0:v>B-25</ns0:v>
-      </ns0:c>
-      <ns0:c r="D37" s="18" t="str">
-        <ns0:v>Data collection, storage and usable availability</ns0:v>
-      </ns0:c>
-      <ns0:c r="E37" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F37" s="18" t="str">
-        <ns0:v>Question explicitly assesses Data collection, storage and usable availability. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G37" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H37" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="38" ht="65" customHeight="1">
-      <ns0:c r="A38" s="18" t="str">
-        <ns0:v>RQ-3114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B38" s="18" t="n">
-        <ns0:v>2134</ns0:v>
-      </ns0:c>
-      <ns0:c r="C38" s="18" t="str">
-        <ns0:v>B-27</ns0:v>
-      </ns0:c>
-      <ns0:c r="D38" s="18" t="str">
-        <ns0:v>Data architecture, access and controls</ns0:v>
-      </ns0:c>
-      <ns0:c r="E38" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F38" s="18" t="str">
-        <ns0:v>Question explicitly assesses Data architecture, access and controls. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G38" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H38" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="39" ht="65" customHeight="1">
-      <ns0:c r="A39" s="18" t="str">
-        <ns0:v>RQ-2231-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B39" s="18" t="n">
-        <ns0:v>2231</ns0:v>
-      </ns0:c>
-      <ns0:c r="C39" s="18" t="str">
-        <ns0:v>B-30</ns0:v>
-      </ns0:c>
-      <ns0:c r="D39" s="18" t="str">
-        <ns0:v>Software stack, tooling and vendor dependency constraints</ns0:v>
-      </ns0:c>
-      <ns0:c r="E39" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F39" s="18" t="str">
-        <ns0:v>Question explicitly assesses Software stack, tooling and vendor dependency constraints. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G39" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H39" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="40" ht="65" customHeight="1">
-      <ns0:c r="A40" s="18" t="str">
-        <ns0:v>RQ-2313-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B40" s="18" t="n">
-        <ns0:v>2313</ns0:v>
-      </ns0:c>
-      <ns0:c r="C40" s="18" t="str">
-        <ns0:v>B-31</ns0:v>
-      </ns0:c>
-      <ns0:c r="D40" s="18" t="str">
-        <ns0:v>Enterprise and asset management system integration</ns0:v>
-      </ns0:c>
-      <ns0:c r="E40" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F40" s="18" t="str">
-        <ns0:v>Question explicitly assesses Enterprise and asset management system integration. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G40" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H40" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="41" ht="65" customHeight="1">
-      <ns0:c r="A41" s="18" t="str">
-        <ns0:v>RQ-2313-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B41" s="18" t="n">
-        <ns0:v>3333</ns0:v>
-      </ns0:c>
-      <ns0:c r="C41" s="18" t="str">
-        <ns0:v>B-33</ns0:v>
-      </ns0:c>
-      <ns0:c r="D41" s="18" t="str">
-        <ns0:v>Maintenance workflow integration and operator feedback loops</ns0:v>
-      </ns0:c>
-      <ns0:c r="E41" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F41" s="18" t="str">
-        <ns0:v>Question explicitly assesses Maintenance workflow integration and operator feedback loops. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G41" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H41" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="42" ht="65" customHeight="1">
-      <ns0:c r="A42" s="18" t="str">
-        <ns0:v>RQ-2323-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B42" s="18" t="n">
-        <ns0:v>2323</ns0:v>
-      </ns0:c>
-      <ns0:c r="C42" s="18" t="str">
-        <ns0:v>B-32</ns0:v>
-      </ns0:c>
-      <ns0:c r="D42" s="18" t="str">
-        <ns0:v>OT, monitoring systems and railway operations integration</ns0:v>
-      </ns0:c>
-      <ns0:c r="E42" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F42" s="18" t="str">
-        <ns0:v>Question explicitly assesses OT, monitoring systems and railway operations integration. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G42" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H42" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="43" ht="65" customHeight="1">
-      <ns0:c r="A43" s="18" t="str">
-        <ns0:v>RQ-2423-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B43" s="18" t="n">
-        <ns0:v>2423</ns0:v>
-      </ns0:c>
-      <ns0:c r="C43" s="18" t="str">
-        <ns0:v>B-35</ns0:v>
-      </ns0:c>
-      <ns0:c r="D43" s="18" t="str">
-        <ns0:v>Unsufficient Model monitoring, -retraining and -evolution</ns0:v>
-      </ns0:c>
-      <ns0:c r="E43" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F43" s="18" t="str">
-        <ns0:v>Question explicitly assesses Unsufficient Model monitoring, -retraining and -evolution. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G43" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H43" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="44" ht="65" customHeight="1">
-      <ns0:c r="A44" s="18" t="str">
-        <ns0:v>RQ-3123-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B44" s="18" t="n">
-        <ns0:v>3123</ns0:v>
-      </ns0:c>
-      <ns0:c r="C44" s="18" t="str">
-        <ns0:v>B-44</ns0:v>
-      </ns0:c>
-      <ns0:c r="D44" s="18" t="str">
-        <ns0:v>Poor solution framing and technology selection</ns0:v>
-      </ns0:c>
-      <ns0:c r="E44" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F44" s="18" t="str">
-        <ns0:v>Question explicitly assesses Poor solution framing and technology selection. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G44" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H44" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="45" ht="65" customHeight="1">
-      <ns0:c r="A45" s="18" t="str">
-        <ns0:v>RQ-3744-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B45" s="18" t="n">
-        <ns0:v>3744</ns0:v>
-      </ns0:c>
-      <ns0:c r="C45" s="18" t="str">
-        <ns0:v>B-21</ns0:v>
-      </ns0:c>
-      <ns0:c r="D45" s="18" t="str">
-        <ns0:v>Safety implications not identified early</ns0:v>
-      </ns0:c>
-      <ns0:c r="E45" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F45" s="18" t="str">
-        <ns0:v>Question explicitly assesses Safety implications not identified early. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G45" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H45" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="46" ht="65" customHeight="1">
-      <ns0:c r="A46" s="18" t="str">
-        <ns0:v>RQ-3744-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B46" s="18" t="n">
-        <ns0:v>3734</ns0:v>
-      </ns0:c>
-      <ns0:c r="C46" s="18"/>
-      <ns0:c r="D46" s="18" t="str">
-        <ns0:v>Difficulty proving safety and reliability at scale</ns0:v>
-      </ns0:c>
-      <ns0:c r="E46" s="18" t="str">
-        <ns0:v>Direct</ns0:v>
-      </ns0:c>
-      <ns0:c r="F46" s="18" t="str">
-        <ns0:v>Question explicitly assesses Difficulty proving safety and reliability at scale. Evaluate its evidence separately within the grouped question.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G46" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H46" s="18" t="str">
-        <ns0:v>Draft semantic mapping. UIC validation is required. Source blocker has no code; numeric ID is authoritative.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="47" ht="65" customHeight="1">
-      <ns0:c r="A47" s="18" t="str">
-        <ns0:v>RQ-1114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B47" s="18" t="n">
-        <ns0:v>1314</ns0:v>
-      </ns0:c>
-      <ns0:c r="C47" s="18" t="str">
-        <ns0:v>B-08</ns0:v>
-      </ns0:c>
-      <ns0:c r="D47" s="18" t="str">
-        <ns0:v>No business ownership beyond prototype</ns0:v>
-      </ns0:c>
-      <ns0:c r="E47" s="18" t="str">
-        <ns0:v>Contextual</ns0:v>
-      </ns0:c>
-      <ns0:c r="F47" s="18" t="str">
-        <ns0:v>Early accountable ownership informs continued ownership beyond the prototype.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G47" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H47" s="18" t="str">
-        <ns0:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="48" ht="65" customHeight="1">
-      <ns0:c r="A48" s="18" t="str">
-        <ns0:v>RQ-1334-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B48" s="18" t="n">
-        <ns0:v>2423</ns0:v>
-      </ns0:c>
-      <ns0:c r="C48" s="18" t="str">
-        <ns0:v>B-35</ns0:v>
-      </ns0:c>
-      <ns0:c r="D48" s="18" t="str">
-        <ns0:v>Unsufficient Model monitoring, -retraining and -evolution</ns0:v>
-      </ns0:c>
-      <ns0:c r="E48" s="18" t="str">
-        <ns0:v>Contextual</ns0:v>
-      </ns0:c>
-      <ns0:c r="F48" s="18" t="str">
-        <ns0:v>The operating model provides context for ongoing model monitoring.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G48" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H48" s="18" t="str">
-        <ns0:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="49" ht="65" customHeight="1">
-      <ns0:c r="A49" s="18" t="str">
-        <ns0:v>RQ-1424-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B49" s="18" t="n">
-        <ns0:v>1413</ns0:v>
-      </ns0:c>
-      <ns0:c r="C49" s="18" t="str">
-        <ns0:v>B-11</ns0:v>
-      </ns0:c>
-      <ns0:c r="D49" s="18" t="str">
-        <ns0:v>Insufficient AI and digital skills across the organisation</ns0:v>
-      </ns0:c>
-      <ns0:c r="E49" s="18" t="str">
-        <ns0:v>Contextual</ns0:v>
-      </ns0:c>
-      <ns0:c r="F49" s="18" t="str">
-        <ns0:v>Interpretation and adoption trials may reveal skills needs.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G49" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H49" s="18" t="str">
-        <ns0:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="50" ht="65" customHeight="1">
-      <ns0:c r="A50" s="18" t="str">
-        <ns0:v>RQ-3114-01</ns0:v>
-      </ns0:c>
-      <ns0:c r="B50" s="18" t="n">
-        <ns0:v>1024</ns0:v>
-      </ns0:c>
-      <ns0:c r="C50" s="18" t="str">
-        <ns0:v>B-39</ns0:v>
-      </ns0:c>
-      <ns0:c r="D50" s="18" t="str">
-        <ns0:v>Inconsistent data quality management across AI use cases</ns0:v>
-      </ns0:c>
-      <ns0:c r="E50" s="18" t="str">
-        <ns0:v>Contextual</ns0:v>
-      </ns0:c>
-      <ns0:c r="F50" s="18" t="str">
-        <ns0:v>Data availability provides context for agreed quality responsibilities and criteria.</ns0:v>
-      </ns0:c>
-      <ns0:c r="G50" s="18" t="str">
-        <ns0:v>Draft - UIC review</ns0:v>
-      </ns0:c>
-      <ns0:c r="H50" s="18" t="str">
-        <ns0:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:dataValidations count="2">
-    <ns0:dataValidation type="list" sqref="G6:G50">
-      <ns0:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</ns0:formula1>
-    </ns0:dataValidation>
-    <ns0:dataValidation type="list" sqref="E6:E50">
-      <ns0:formula1>"Direct,Contextual"</ns0:formula1>
-    </ns0:dataValidation>
-  </ns0:dataValidations>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ns0:tableParts count="1">
-    <ns0:tablePart ns1:id="R700b112c5def4a84"/>
-  </ns0:tableParts>
-</ns0:worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Candidate question-to-blocker mappings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="16" t="str">
+        <x:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>Question_ID</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>Blocker_ID</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>Blocker_Code</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>Blocker_Title</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>Relationship</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>Rationale</x:v>
+      </x:c>
+      <x:c r="G5" s="20" t="str">
+        <x:v>Review_Status</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="str">
+        <x:v>Review_Comments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="65" customHeight="1">
+      <x:c r="A6" s="18" t="str">
+        <x:v>RQ-1114-01</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="n">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>B-01</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>Technology-push AI initiatives without clear ownership</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F6" s="18" t="str">
+        <x:v>Question explicitly assesses Technology-push AI initiatives without clear ownership. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H6" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="65" customHeight="1">
+      <x:c r="A7" s="18" t="str">
+        <x:v>RQ-1114-01</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>B-04</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>Lack of shared AI vision</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="str">
+        <x:v>Question explicitly assesses Lack of shared AI vision. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G7" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H7" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="65" customHeight="1">
+      <x:c r="A8" s="18" t="str">
+        <x:v>RQ-1133-01</x:v>
+      </x:c>
+      <x:c r="B8" s="18" t="n">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>B-02</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>Unclear value articulation for stakeholder groups</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F8" s="18" t="str">
+        <x:v>Question explicitly assesses Unclear value articulation for stakeholder groups. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G8" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H8" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="65" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>RQ-1143-01</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="n">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>B-03</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>Unclear financial implications, risks and investment logic</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="str">
+        <x:v>Question explicitly assesses Unclear financial implications, risks and investment logic. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H9" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="65" customHeight="1">
+      <x:c r="A10" s="18" t="str">
+        <x:v>RQ-1223-01</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="n">
+        <x:v>1223</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>B-05</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>Fragmented AI priorities across silos</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="str">
+        <x:v>Question explicitly assesses Fragmented AI priorities across silos. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H10" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="65" customHeight="1">
+      <x:c r="A11" s="18" t="str">
+        <x:v>RQ-1233-01</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="n">
+        <x:v>1233</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>B-06</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>Slow or unclear AI governance</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="str">
+        <x:v>Question explicitly assesses Slow or unclear AI governance. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H11" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="65" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>RQ-1233-01</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="n">
+        <x:v>1823</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>B-23</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>There is no shared understanding of AI project maturity and readiness across teams and decision-makers.</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="str">
+        <x:v>Question explicitly assesses There is no shared understanding of AI project maturity and readiness across teams and decision-makers.. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H12" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="65" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>RQ-1243-01</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="n">
+        <x:v>1243</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>B-07</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>Insufficient sustained management commitment 'towards the end goal'</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>Question explicitly assesses Insufficient sustained management commitment 'towards the end goal'. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H13" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="65" customHeight="1">
+      <x:c r="A14" s="18" t="str">
+        <x:v>RQ-1314-01</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>B-08</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>No business ownership beyond prototype</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="str">
+        <x:v>Question explicitly assesses No business ownership beyond prototype. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H14" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="65" customHeight="1">
+      <x:c r="A15" s="18" t="str">
+        <x:v>RQ-1314-01</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="n">
+        <x:v>1323</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>B-09</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>Unclear human accountability in AI-supported operational decisions</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="str">
+        <x:v>Question explicitly assesses Unclear human accountability in AI-supported operational decisions. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H15" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="65" customHeight="1">
+      <x:c r="A16" s="18" t="str">
+        <x:v>RQ-1334-01</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="n">
+        <x:v>1334</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>B-10</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="str">
+        <x:v>No defined run model after go-live</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="str">
+        <x:v>Question explicitly assesses No defined run model after go-live. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H16" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="65" customHeight="1">
+      <x:c r="A17" s="18" t="str">
+        <x:v>RQ-1334-01</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="n">
+        <x:v>3413</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>B-34</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="str">
+        <x:v>Production-grade AI operations and handover gap</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="str">
+        <x:v>Question explicitly assesses Production-grade AI operations and handover gap. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H17" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="18" t="str">
+        <x:v>RQ-1413-01</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="n">
+        <x:v>1413</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>B-11</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>Insufficient AI and digital skills across the organisation</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="str">
+        <x:v>Question explicitly assesses Insufficient AI and digital skills across the organisation. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H18" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="18" t="str">
+        <x:v>RQ-1424-01</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="n">
+        <x:v>1424</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>B-12</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="str">
+        <x:v>Low trust and cultural resistance to AI</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="str">
+        <x:v>Question explicitly assesses Low trust and cultural resistance to AI. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H19" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="65" customHeight="1">
+      <x:c r="A20" s="18" t="str">
+        <x:v>RQ-1424-01</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="n">
+        <x:v>3523</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>B-37</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="str">
+        <x:v>Limited explainability, interpretability and field trust</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="str">
+        <x:v>Question explicitly assesses Limited explainability, interpretability and field trust. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H20" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="65" customHeight="1">
+      <x:c r="A21" s="18" t="str">
+        <x:v>RQ-1433-01</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="n">
+        <x:v>1433</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>B-13</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="str">
+        <x:v>Limited capacity to absorb continuous change</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="str">
+        <x:v>Question explicitly assesses Limited capacity to absorb continuous change. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H21" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="65" customHeight="1">
+      <x:c r="A22" s="18" t="str">
+        <x:v>RQ-1511-01</x:v>
+      </x:c>
+      <x:c r="B22" s="18" t="n">
+        <x:v>1511</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>B-14</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>Unrealistic understanding of AI capabilities and limits among decision-makers</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>Question explicitly assesses Unrealistic understanding of AI capabilities and limits among decision-makers. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H22" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="65" customHeight="1">
+      <x:c r="A23" s="18" t="str">
+        <x:v>RQ-1524-01</x:v>
+      </x:c>
+      <x:c r="B23" s="18" t="n">
+        <x:v>1524</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>B-15</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>Solutions misaligned with operational context</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="str">
+        <x:v>Question explicitly assesses Solutions misaligned with operational context. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H23" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="65" customHeight="1">
+      <x:c r="A24" s="18" t="str">
+        <x:v>RQ-1614-01</x:v>
+      </x:c>
+      <x:c r="B24" s="18" t="n">
+        <x:v>1614</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>B-16</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="str">
+        <x:v>Fragmented or restrictive data governance</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="str">
+        <x:v>Question explicitly assesses Fragmented or restrictive data governance. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H24" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="65" customHeight="1">
+      <x:c r="A25" s="18" t="str">
+        <x:v>RQ-1614-01</x:v>
+      </x:c>
+      <x:c r="B25" s="18" t="n">
+        <x:v>3634</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>B-18</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>Organisational data silos limiting reuse and scaling</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>Question explicitly assesses Organisational data silos limiting reuse and scaling. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="65" customHeight="1">
+      <x:c r="A26" s="18" t="str">
+        <x:v>RQ-1713-01</x:v>
+      </x:c>
+      <x:c r="B26" s="18" t="n">
+        <x:v>1713</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="str">
+        <x:v>B-19</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="str">
+        <x:v>Limited AI expertise in legal functions</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F26" s="18" t="str">
+        <x:v>Question explicitly assesses Limited AI expertise in legal functions. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G26" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H26" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="65" customHeight="1">
+      <x:c r="A27" s="18" t="str">
+        <x:v>RQ-1713-01</x:v>
+      </x:c>
+      <x:c r="B27" s="18" t="n">
+        <x:v>1723</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>B-20</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>Unclear regulatory interpretation increases perceived risk</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F27" s="18" t="str">
+        <x:v>Question explicitly assesses Unclear regulatory interpretation increases perceived risk. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G27" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="65" customHeight="1">
+      <x:c r="A28" s="18" t="str">
+        <x:v>RQ-1811-01</x:v>
+      </x:c>
+      <x:c r="B28" s="18" t="n">
+        <x:v>1811</x:v>
+      </x:c>
+      <x:c r="C28" s="18" t="str">
+        <x:v>B-22</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="str">
+        <x:v>Ambiguous definition of scaling</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F28" s="18" t="str">
+        <x:v>Question explicitly assesses Ambiguous definition of scaling. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G28" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H28" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="65" customHeight="1">
+      <x:c r="A29" s="18" t="str">
+        <x:v>RQ-1811-01</x:v>
+      </x:c>
+      <x:c r="B29" s="18" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="str">
+        <x:v>B-36</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>Model performance degrades with scale</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>Question explicitly assesses Model performance degrades with scale. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="65" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>RQ-1043-01</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="n">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="str">
+        <x:v>B-40</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>Weak MVP and incremental delivery discipline</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F30" s="18" t="str">
+        <x:v>Question explicitly assesses Weak MVP and incremental delivery discipline. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G30" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H30" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="65" customHeight="1">
+      <x:c r="A31" s="18" t="str">
+        <x:v>RQ-1043-01</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="n">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="str">
+        <x:v>B-24</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="str">
+        <x:v>PoC to production transition stalls</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>Question explicitly assesses PoC to production transition stalls. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G31" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H31" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="65" customHeight="1">
+      <x:c r="A32" s="18" t="str">
+        <x:v>RQ-1043-01</x:v>
+      </x:c>
+      <x:c r="B32" s="18" t="n">
+        <x:v>1921</x:v>
+      </x:c>
+      <x:c r="C32" s="18" t="str">
+        <x:v>B-42</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="str">
+        <x:v>Unrealistic delivery timelines and scaling ambition</x:v>
+      </x:c>
+      <x:c r="E32" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F32" s="18" t="str">
+        <x:v>Question explicitly assesses Unrealistic delivery timelines and scaling ambition. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G32" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H32" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="65" customHeight="1">
+      <x:c r="A33" s="18" t="str">
+        <x:v>RQ-2213-01</x:v>
+      </x:c>
+      <x:c r="B33" s="18" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="C33" s="18" t="str">
+        <x:v>B-28</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="str">
+        <x:v>Immature platform architecture and fragmented IT foundations</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F33" s="18" t="str">
+        <x:v>Question explicitly assesses Immature platform architecture and fragmented IT foundations. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G33" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H33" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="65" customHeight="1">
+      <x:c r="A34" s="18" t="str">
+        <x:v>RQ-2213-01</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="n">
+        <x:v>2221</x:v>
+      </x:c>
+      <x:c r="C34" s="18" t="str">
+        <x:v>B-29</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="str">
+        <x:v>Compute environment constraints for AI deployment</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F34" s="18" t="str">
+        <x:v>Question explicitly assesses Compute environment constraints for AI deployment. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G34" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H34" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="65" customHeight="1">
+      <x:c r="A35" s="18" t="str">
+        <x:v>RQ-1024-01</x:v>
+      </x:c>
+      <x:c r="B35" s="18" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="C35" s="18" t="str">
+        <x:v>B-39</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="str">
+        <x:v>Inconsistent data quality management across AI use cases</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F35" s="18" t="str">
+        <x:v>Question explicitly assesses Inconsistent data quality management across AI use cases. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G35" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H35" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="65" customHeight="1">
+      <x:c r="A36" s="18" t="str">
+        <x:v>RQ-1024-01</x:v>
+      </x:c>
+      <x:c r="B36" s="18" t="n">
+        <x:v>2123</x:v>
+      </x:c>
+      <x:c r="C36" s="18" t="str">
+        <x:v>B-26</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="str">
+        <x:v>Data quality, consistency and semantic structure</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F36" s="18" t="str">
+        <x:v>Question explicitly assesses Data quality, consistency and semantic structure. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G36" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H36" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="65" customHeight="1">
+      <x:c r="A37" s="18" t="str">
+        <x:v>RQ-3114-01</x:v>
+      </x:c>
+      <x:c r="B37" s="18" t="n">
+        <x:v>3114</x:v>
+      </x:c>
+      <x:c r="C37" s="18" t="str">
+        <x:v>B-25</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="str">
+        <x:v>Data collection, storage and usable availability</x:v>
+      </x:c>
+      <x:c r="E37" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F37" s="18" t="str">
+        <x:v>Question explicitly assesses Data collection, storage and usable availability. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G37" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H37" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="65" customHeight="1">
+      <x:c r="A38" s="18" t="str">
+        <x:v>RQ-3114-01</x:v>
+      </x:c>
+      <x:c r="B38" s="18" t="n">
+        <x:v>2134</x:v>
+      </x:c>
+      <x:c r="C38" s="18" t="str">
+        <x:v>B-27</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="str">
+        <x:v>Data architecture, access and controls</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F38" s="18" t="str">
+        <x:v>Question explicitly assesses Data architecture, access and controls. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G38" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H38" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="65" customHeight="1">
+      <x:c r="A39" s="18" t="str">
+        <x:v>RQ-2231-01</x:v>
+      </x:c>
+      <x:c r="B39" s="18" t="n">
+        <x:v>2231</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="str">
+        <x:v>B-30</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="str">
+        <x:v>Software stack, tooling and vendor dependency constraints</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F39" s="18" t="str">
+        <x:v>Question explicitly assesses Software stack, tooling and vendor dependency constraints. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G39" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H39" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="65" customHeight="1">
+      <x:c r="A40" s="18" t="str">
+        <x:v>RQ-2313-01</x:v>
+      </x:c>
+      <x:c r="B40" s="18" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="str">
+        <x:v>B-31</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="str">
+        <x:v>Enterprise and asset management system integration</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F40" s="18" t="str">
+        <x:v>Question explicitly assesses Enterprise and asset management system integration. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G40" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H40" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="65" customHeight="1">
+      <x:c r="A41" s="18" t="str">
+        <x:v>RQ-2313-01</x:v>
+      </x:c>
+      <x:c r="B41" s="18" t="n">
+        <x:v>3333</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="str">
+        <x:v>B-33</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="str">
+        <x:v>Maintenance workflow integration and operator feedback loops</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F41" s="18" t="str">
+        <x:v>Question explicitly assesses Maintenance workflow integration and operator feedback loops. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G41" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H41" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="65" customHeight="1">
+      <x:c r="A42" s="18" t="str">
+        <x:v>RQ-2323-01</x:v>
+      </x:c>
+      <x:c r="B42" s="18" t="n">
+        <x:v>2323</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="str">
+        <x:v>B-32</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="str">
+        <x:v>OT, monitoring systems and railway operations integration</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F42" s="18" t="str">
+        <x:v>Question explicitly assesses OT, monitoring systems and railway operations integration. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G42" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H42" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="65" customHeight="1">
+      <x:c r="A43" s="18" t="str">
+        <x:v>RQ-2423-01</x:v>
+      </x:c>
+      <x:c r="B43" s="18" t="n">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="C43" s="18" t="str">
+        <x:v>B-35</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="str">
+        <x:v>Unsufficient Model monitoring, -retraining and -evolution</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F43" s="18" t="str">
+        <x:v>Question explicitly assesses Unsufficient Model monitoring, -retraining and -evolution. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G43" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H43" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="65" customHeight="1">
+      <x:c r="A44" s="18" t="str">
+        <x:v>RQ-3123-01</x:v>
+      </x:c>
+      <x:c r="B44" s="18" t="n">
+        <x:v>3123</x:v>
+      </x:c>
+      <x:c r="C44" s="18" t="str">
+        <x:v>B-44</x:v>
+      </x:c>
+      <x:c r="D44" s="18" t="str">
+        <x:v>Poor solution framing and technology selection</x:v>
+      </x:c>
+      <x:c r="E44" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F44" s="18" t="str">
+        <x:v>Question explicitly assesses Poor solution framing and technology selection. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G44" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H44" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="65" customHeight="1">
+      <x:c r="A45" s="18" t="str">
+        <x:v>RQ-3744-01</x:v>
+      </x:c>
+      <x:c r="B45" s="18" t="n">
+        <x:v>3744</x:v>
+      </x:c>
+      <x:c r="C45" s="18" t="str">
+        <x:v>B-21</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="str">
+        <x:v>Safety implications not identified early</x:v>
+      </x:c>
+      <x:c r="E45" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F45" s="18" t="str">
+        <x:v>Question explicitly assesses Safety implications not identified early. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G45" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H45" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="65" customHeight="1">
+      <x:c r="A46" s="18" t="str">
+        <x:v>RQ-3744-01</x:v>
+      </x:c>
+      <x:c r="B46" s="18" t="n">
+        <x:v>3734</x:v>
+      </x:c>
+      <x:c r="C46" s="18"/>
+      <x:c r="D46" s="18" t="str">
+        <x:v>Difficulty proving safety and reliability at scale</x:v>
+      </x:c>
+      <x:c r="E46" s="18" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="F46" s="18" t="str">
+        <x:v>Question explicitly assesses Difficulty proving safety and reliability at scale. Evaluate its evidence separately within the grouped question.</x:v>
+      </x:c>
+      <x:c r="G46" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H46" s="18" t="str">
+        <x:v>Draft semantic mapping. UIC validation is required. Source blocker has no code; numeric ID is authoritative.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="65" customHeight="1">
+      <x:c r="A47" s="18" t="str">
+        <x:v>RQ-1114-01</x:v>
+      </x:c>
+      <x:c r="B47" s="18" t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="C47" s="18" t="str">
+        <x:v>B-08</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="str">
+        <x:v>No business ownership beyond prototype</x:v>
+      </x:c>
+      <x:c r="E47" s="18" t="str">
+        <x:v>Contextual</x:v>
+      </x:c>
+      <x:c r="F47" s="18" t="str">
+        <x:v>Early accountable ownership informs continued ownership beyond the prototype.</x:v>
+      </x:c>
+      <x:c r="G47" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H47" s="18" t="str">
+        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="65" customHeight="1">
+      <x:c r="A48" s="18" t="str">
+        <x:v>RQ-1334-01</x:v>
+      </x:c>
+      <x:c r="B48" s="18" t="n">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="C48" s="18" t="str">
+        <x:v>B-35</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="str">
+        <x:v>Unsufficient Model monitoring, -retraining and -evolution</x:v>
+      </x:c>
+      <x:c r="E48" s="18" t="str">
+        <x:v>Contextual</x:v>
+      </x:c>
+      <x:c r="F48" s="18" t="str">
+        <x:v>The operating model provides context for ongoing model monitoring.</x:v>
+      </x:c>
+      <x:c r="G48" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H48" s="18" t="str">
+        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="65" customHeight="1">
+      <x:c r="A49" s="18" t="str">
+        <x:v>RQ-1424-01</x:v>
+      </x:c>
+      <x:c r="B49" s="18" t="n">
+        <x:v>1413</x:v>
+      </x:c>
+      <x:c r="C49" s="18" t="str">
+        <x:v>B-11</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="str">
+        <x:v>Insufficient AI and digital skills across the organisation</x:v>
+      </x:c>
+      <x:c r="E49" s="18" t="str">
+        <x:v>Contextual</x:v>
+      </x:c>
+      <x:c r="F49" s="18" t="str">
+        <x:v>Interpretation and adoption trials may reveal skills needs.</x:v>
+      </x:c>
+      <x:c r="G49" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H49" s="18" t="str">
+        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="65" customHeight="1">
+      <x:c r="A50" s="18" t="str">
+        <x:v>RQ-3114-01</x:v>
+      </x:c>
+      <x:c r="B50" s="18" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="C50" s="18" t="str">
+        <x:v>B-39</x:v>
+      </x:c>
+      <x:c r="D50" s="18" t="str">
+        <x:v>Inconsistent data quality management across AI use cases</x:v>
+      </x:c>
+      <x:c r="E50" s="18" t="str">
+        <x:v>Contextual</x:v>
+      </x:c>
+      <x:c r="F50" s="18" t="str">
+        <x:v>Data availability provides context for agreed quality responsibilities and criteria.</x:v>
+      </x:c>
+      <x:c r="G50" s="18" t="str">
+        <x:v>Draft - UIC review</x:v>
+      </x:c>
+      <x:c r="H50" s="18" t="str">
+        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="G6:G50">
+      <x:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E50">
+      <x:formula1>"Direct,Contextual"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700b112c5def4a84"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Final_Blockers&Enablers_Explorer.xlsx
+++ b/data/Final_Blockers&Enablers_Explorer.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Blocker_Dependency_map" sheetId="7" r:id="rId2"/>
     <sheet name="Enablers" sheetId="10" r:id="rId3"/>
     <sheet name="Enablers_Dependency_Map" sheetId="11" r:id="rId4"/>
-    <sheet name="Readiness_Questions" sheetId="12" r:id="rId11"/>
-    <sheet name="Question_Blocker_Map" sheetId="13" r:id="rId12"/>
+    <sheet name="Readiness_Questions" sheetId="12" state="visible" r:id="rId11"/>
+    <sheet name="Question_Blocker_Map" sheetId="13" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blockers!$A$1:$L$42</definedName>
@@ -3155,23 +3155,26 @@
       <family val="2"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3200,14 +3203,14 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24476A"/>
+        <fgColor rgb="0024476A"/>
       </patternFill>
     </fill>
   </fills>
@@ -3244,7 +3247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3282,21 +3285,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3356,39 +3352,41 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReadinessQuestions" displayName="ReadinessQuestions" ref="A5:L31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="12">
-    <x:tableColumn id="1" name="Question_ID"/>
-    <x:tableColumn id="2" name="Question"/>
-    <x:tableColumn id="3" name="Dimension"/>
-    <x:tableColumn id="4" name="Lifecycle_Stage"/>
-    <x:tableColumn id="5" name="Provisional_Stage_Gate"/>
-    <x:tableColumn id="6" name="Guidance"/>
-    <x:tableColumn id="7" name="Evidence_Examples"/>
-    <x:tableColumn id="8" name="Applicability"/>
-    <x:tableColumn id="9" name="Review_Status"/>
-    <x:tableColumn id="10" name="Review_Comments"/>
-    <x:tableColumn id="11" name="Source_Blocker_IDs"/>
-    <x:tableColumn id="12" name="Source_Stage_Gates"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReadinessQuestions" displayName="ReadinessQuestions" ref="A5:L31" headerRowCount="1">
+  <autoFilter ref="A5:L31"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Question_ID"/>
+    <tableColumn id="2" name="Question"/>
+    <tableColumn id="3" name="Dimension"/>
+    <tableColumn id="4" name="Lifecycle_Stage"/>
+    <tableColumn id="5" name="Provisional_Stage_Gate"/>
+    <tableColumn id="6" name="Guidance"/>
+    <tableColumn id="7" name="Evidence_Examples"/>
+    <tableColumn id="8" name="Applicability"/>
+    <tableColumn id="9" name="Review_Status"/>
+    <tableColumn id="10" name="Review_Comments"/>
+    <tableColumn id="11" name="Source_Blocker_IDs"/>
+    <tableColumn id="12" name="Source_Stage_Gates"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="QuestionBlockerMap" displayName="QuestionBlockerMap" ref="A5:H50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="Question_ID"/>
-    <x:tableColumn id="2" name="Blocker_ID"/>
-    <x:tableColumn id="3" name="Blocker_Code"/>
-    <x:tableColumn id="4" name="Blocker_Title"/>
-    <x:tableColumn id="5" name="Relationship"/>
-    <x:tableColumn id="6" name="Rationale"/>
-    <x:tableColumn id="7" name="Review_Status"/>
-    <x:tableColumn id="8" name="Review_Comments"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="QuestionBlockerMap" displayName="QuestionBlockerMap" ref="A5:H50" headerRowCount="1">
+  <autoFilter ref="A5:H50"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Question_ID"/>
+    <tableColumn id="2" name="Blocker_ID"/>
+    <tableColumn id="3" name="Blocker_Code"/>
+    <tableColumn id="4" name="Blocker_Title"/>
+    <tableColumn id="5" name="Relationship"/>
+    <tableColumn id="6" name="Rationale"/>
+    <tableColumn id="7" name="Review_Status"/>
+    <tableColumn id="8" name="Review_Comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5200,2314 +5198,3576 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="55" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="65" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="21" t="str">
-        <x:v>Candidate AI project readiness questions</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="16" t="str">
-        <x:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="16" t="str">
-        <x:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="20" t="str">
-        <x:v>Question_ID</x:v>
-      </x:c>
-      <x:c r="B5" s="20" t="str">
-        <x:v>Question</x:v>
-      </x:c>
-      <x:c r="C5" s="20" t="str">
-        <x:v>Dimension</x:v>
-      </x:c>
-      <x:c r="D5" s="20" t="str">
-        <x:v>Lifecycle_Stage</x:v>
-      </x:c>
-      <x:c r="E5" s="20" t="str">
-        <x:v>Provisional_Stage_Gate</x:v>
-      </x:c>
-      <x:c r="F5" s="20" t="str">
-        <x:v>Guidance</x:v>
-      </x:c>
-      <x:c r="G5" s="20" t="str">
-        <x:v>Evidence_Examples</x:v>
-      </x:c>
-      <x:c r="H5" s="20" t="str">
-        <x:v>Applicability</x:v>
-      </x:c>
-      <x:c r="I5" s="20" t="str">
-        <x:v>Review_Status</x:v>
-      </x:c>
-      <x:c r="J5" s="20" t="str">
-        <x:v>Review_Comments</x:v>
-      </x:c>
-      <x:c r="K5" s="20" t="str">
-        <x:v>Source_Blocker_IDs</x:v>
-      </x:c>
-      <x:c r="L5" s="20" t="str">
-        <x:v>Source_Stage_Gates</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="85" customHeight="1">
-      <x:c r="A6" s="18" t="str">
-        <x:v>RQ-1114-01</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
-        <x:v>Is the project anchored in a validated operational problem, an accountable owner and the shared AI vision?</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E6" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="str">
-        <x:v>Confirm problem evidence, ownership and strategic alignment separately. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G6" s="18" t="str">
-        <x:v>Problem baseline; owner approval; AI strategy alignment.</x:v>
-      </x:c>
-      <x:c r="H6" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I6" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J6" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K6" s="18" t="str">
-        <x:v>1114; 1211</x:v>
-      </x:c>
-      <x:c r="L6" s="18" t="str">
-        <x:v>1114: Gate 0-Strategic Alignment &amp; Idea Validation; 1211: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="85" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>RQ-1133-01</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Is the expected value clear to each affected stakeholder group?</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>Separate benefits for maintenance, asset management, operations and leadership. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str">
-        <x:v>Stakeholder value statements; interviews; benefit measures.</x:v>
-      </x:c>
-      <x:c r="H7" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I7" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J7" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="str">
-        <x:v>1133</x:v>
-      </x:c>
-      <x:c r="L7" s="18" t="str">
-        <x:v>1133: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="85" customHeight="1">
-      <x:c r="A8" s="18" t="str">
-        <x:v>RQ-1143-01</x:v>
-      </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>Does the business case address costs, benefits, risks and funding of shared foundations?</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="18" t="str">
-        <x:v>Distinguish use-case costs from reusable platform, data and governance investments. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G8" s="18" t="str">
-        <x:v>Cost model; risk register; shared investment allocation.</x:v>
-      </x:c>
-      <x:c r="H8" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I8" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J8" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K8" s="18" t="str">
-        <x:v>1143</x:v>
-      </x:c>
-      <x:c r="L8" s="18" t="str">
-        <x:v>1143: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="85" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>RQ-1223-01</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Have cross-functional priorities and competing AI initiatives been reconciled?</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
-        <x:v>Identify duplicated work and portfolio-level resource conflicts. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="str">
-        <x:v>Portfolio review; prioritisation decisions; resource commitments.</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I9" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K9" s="18" t="str">
-        <x:v>1223</x:v>
-      </x:c>
-      <x:c r="L9" s="18" t="str">
-        <x:v>1223: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="85" customHeight="1">
-      <x:c r="A10" s="18" t="str">
-        <x:v>RQ-1233-01</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="str">
-        <x:v>Do teams share evidence-based readiness criteria, decision rights and a timely review process?</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E10" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="18" t="str">
-        <x:v>Document readiness criteria, reviewers, approval authority and decision deadlines. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G10" s="18" t="str">
-        <x:v>Readiness checklist; governance charter; decision matrix; review calendar.</x:v>
-      </x:c>
-      <x:c r="H10" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I10" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="str">
-        <x:v>1233; 1823</x:v>
-      </x:c>
-      <x:c r="L10" s="18" t="str">
-        <x:v>1233: Gate 0-Strategic Alignment &amp; Idea Validation; 1823: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="85" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>RQ-1243-01</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Is management sponsorship and funding sustained through deployment and operation?</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="str">
-        <x:v>Confirm commitments beyond the pilot and arrangements for recurring reviews. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="str">
-        <x:v>Sponsor commitments; funding plan; steering review minutes.</x:v>
-      </x:c>
-      <x:c r="H11" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I11" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="str">
-        <x:v>1243</x:v>
-      </x:c>
-      <x:c r="L11" s="18" t="str">
-        <x:v>1243: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="85" customHeight="1">
-      <x:c r="A12" s="18" t="str">
-        <x:v>RQ-1314-01</x:v>
-      </x:c>
-      <x:c r="B12" s="18" t="str">
-        <x:v>Are business ownership and human accountability defined for operational use beyond the prototype?</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="str">
-        <x:v>Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-      <x:c r="E12" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F12" s="18" t="str">
-        <x:v>Confirm benefit ownership and responsibilities for judgement, approval, action and escalation. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G12" s="18" t="str">
-        <x:v>Ownership agreement; decision workflow; responsibility matrix; escalation procedure.</x:v>
-      </x:c>
-      <x:c r="H12" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I12" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="str">
-        <x:v>1314; 1323</x:v>
-      </x:c>
-      <x:c r="L12" s="18" t="str">
-        <x:v>1314: Gate 3- Operational Deployment &amp; Commissioning; 1323: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="85" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>RQ-1334-01</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Has the production operating model been funded and accepted through a reproducible deployment and support handover?</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Organisational; Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F13" s="18" t="str">
-        <x:v>Check support ownership, monitoring, incidents, deployment reproducibility and handover acceptance. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G13" s="18" t="str">
-        <x:v>Run budget; support acceptance; deployment records; telemetry and recovery tests.</x:v>
-      </x:c>
-      <x:c r="H13" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I13" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="str">
-        <x:v>1334; 3413</x:v>
-      </x:c>
-      <x:c r="L13" s="18" t="str">
-        <x:v>1334: Gate 3- Operational Deployment &amp; Commissioning; 3413: Gate 4-Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="85" customHeight="1">
-      <x:c r="A14" s="18" t="str">
-        <x:v>RQ-1413-01</x:v>
-      </x:c>
-      <x:c r="B14" s="18" t="str">
-        <x:v>Do affected teams have the skills to interpret, challenge and use AI outputs?</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="str">
-        <x:v>Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="str">
-        <x:v>Assess role-specific competence and address training gaps. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="str">
-        <x:v>Skills assessment; training plan; competence demonstration.</x:v>
-      </x:c>
-      <x:c r="H14" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I14" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="str">
-        <x:v>1413</x:v>
-      </x:c>
-      <x:c r="L14" s="18" t="str">
-        <x:v>1413: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="85" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>RQ-1424-01</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>Have field users demonstrated that they can understand, challenge and use the AI outputs, with adoption concerns addressed?</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Organisational; Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str">
-        <x:v>Assess interpretation and trust with affected users. Record unresolved concerns and workflow burden. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G15" s="18" t="str">
-        <x:v>User interpretation trials; explanation examples; co-design and adoption feedback.</x:v>
-      </x:c>
-      <x:c r="H15" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I15" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="str">
-        <x:v>1424; 3523</x:v>
-      </x:c>
-      <x:c r="L15" s="18" t="str">
-        <x:v>1424: Gate 0-Strategic Alignment &amp; Idea Validation; 3523: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="85" customHeight="1">
-      <x:c r="A16" s="18" t="str">
-        <x:v>RQ-1433-01</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="str">
-        <x:v>Can the organisation absorb iterative releases and transition to changed AI capabilities?</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="str">
-        <x:v>Retirement &amp; Transition</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="str">
-        <x:v>Assess change capacity across releases and eventual replacement or retirement. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G16" s="18" t="str">
-        <x:v>Change capacity assessment; release plan; transition and training plan.</x:v>
-      </x:c>
-      <x:c r="H16" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I16" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="str">
-        <x:v>Source assigns Gate 5. Review earlier lifecycle applicability. UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="str">
-        <x:v>1433</x:v>
-      </x:c>
-      <x:c r="L16" s="18" t="str">
-        <x:v>1433: Gate 5-Retirement &amp; Transition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="85" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>RQ-1511-01</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
-        <x:v>Do decision-makers understand the proposed AI capability, data needs and limitations?</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="18" t="str">
-        <x:v>Test expectations against realistic operational conditions and assurance needs. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G17" s="18" t="str">
-        <x:v>Capability briefing; limitations register; feasibility evidence.</x:v>
-      </x:c>
-      <x:c r="H17" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I17" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="str">
-        <x:v>1511</x:v>
-      </x:c>
-      <x:c r="L17" s="18" t="str">
-        <x:v>1511: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="85" customHeight="1">
-      <x:c r="A18" s="18" t="str">
-        <x:v>RQ-1524-01</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="str">
-        <x:v>Does the proposed solution fit real railway field conditions and support needs?</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E18" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F18" s="18" t="str">
-        <x:v>Consider possession windows, connectivity, shifts and maintenance practices. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G18" s="18" t="str">
-        <x:v>Field workflow observations; operational requirements; support assessment.</x:v>
-      </x:c>
-      <x:c r="H18" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I18" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="str">
-        <x:v>1524</x:v>
-      </x:c>
-      <x:c r="L18" s="18" t="str">
-        <x:v>1524: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="85" customHeight="1">
-      <x:c r="A19" s="18" t="str">
-        <x:v>RQ-1614-01</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="str">
-        <x:v>Are cross-unit data ownership, access rules and sharing arrangements usable for reuse beyond the local pilot?</x:v>
-      </x:c>
-      <x:c r="C19" s="18" t="str">
-        <x:v>Organisational; Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E19" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="str">
-        <x:v>Confirm governance and practical access across silos, including interoperability and control responsibilities. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G19" s="18" t="str">
-        <x:v>Data sharing agreements; access approvals; cross-unit reuse trial; governance decision records.</x:v>
-      </x:c>
-      <x:c r="H19" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I19" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="str">
-        <x:v>1614; 3634</x:v>
-      </x:c>
-      <x:c r="L19" s="18" t="str">
-        <x:v>1614: Gate 0-Strategic Alignment &amp; Idea Validation; 3634: Gate 0-Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="85" customHeight="1">
-      <x:c r="A20" s="18" t="str">
-        <x:v>RQ-1713-01</x:v>
-      </x:c>
-      <x:c r="B20" s="18" t="str">
-        <x:v>Has a suitably informed legal team assessed applicable requirements and unresolved regulatory interpretations?</x:v>
-      </x:c>
-      <x:c r="C20" s="18" t="str">
-        <x:v>Organisational</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="str">
-        <x:v>Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-      <x:c r="E20" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" s="18" t="str">
-        <x:v>Confirm specialist capability, document interpretations and assign owners to unresolved questions. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G20" s="18" t="str">
-        <x:v>Legal assessment; specialist input; requirements register; unresolved issue log.</x:v>
-      </x:c>
-      <x:c r="H20" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I20" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="str">
-        <x:v>1713; 1723</x:v>
-      </x:c>
-      <x:c r="L20" s="18" t="str">
-        <x:v>1713: Gate 1-Solution Architecture &amp; Feasibility; 1723: Gate 1-Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="85" customHeight="1">
-      <x:c r="A21" s="18" t="str">
-        <x:v>RQ-1811-01</x:v>
-      </x:c>
-      <x:c r="B21" s="18" t="str">
-        <x:v>Is the intended scale defined, and is model performance demonstrated across that scope and operational variation?</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="str">
-        <x:v>Organisational; Technical</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E21" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F21" s="18" t="str">
-        <x:v>Define sites, assets, users and workloads, then test false positives, missed detections and segment performance. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G21" s="18" t="str">
-        <x:v>Scaling scope; volume assumptions; segment validation results; acceptance thresholds.</x:v>
-      </x:c>
-      <x:c r="H21" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I21" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="str">
-        <x:v>1811; 2513</x:v>
-      </x:c>
-      <x:c r="L21" s="18" t="str">
-        <x:v>1811: Gate 2- Solution Build &amp; Verification; 2513: Gate 4-Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="85" customHeight="1">
-      <x:c r="A22" s="18" t="str">
-        <x:v>RQ-1043-01</x:v>
-      </x:c>
-      <x:c r="B22" s="18" t="str">
-        <x:v>Is there a realistic incremental pathway from MVP and PoC to production, with owners and evidence at each milestone?</x:v>
-      </x:c>
-      <x:c r="C22" s="18" t="str">
-        <x:v>Organisational; Technical</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="str">
-        <x:v>Strategic Alignment &amp; Idea Validation</x:v>
-      </x:c>
-      <x:c r="E22" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F22" s="18" t="str">
-        <x:v>Assess increments, transition work, integration and assurance dependencies, resources and approval lead times. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G22" s="18" t="str">
-        <x:v>MVP roadmap; production transition plan; integrated schedule; field validation milestones.</x:v>
-      </x:c>
-      <x:c r="H22" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I22" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="str">
-        <x:v>1043; 1833; 1921</x:v>
-      </x:c>
-      <x:c r="L22" s="18" t="str">
-        <x:v>1043: Gate 0-Strategic Alignment &amp; Idea Validation; 1833: Gate 0-Strategic Alignment &amp; Idea Validation; 1921: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="85" customHeight="1">
-      <x:c r="A23" s="18" t="str">
-        <x:v>RQ-2213-01</x:v>
-      </x:c>
-      <x:c r="B23" s="18" t="str">
-        <x:v>Can the governed platform and compute environment sustain the intended workload and operational constraints?</x:v>
-      </x:c>
-      <x:c r="C23" s="18" t="str">
-        <x:v>Technical</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E23" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F23" s="18" t="str">
-        <x:v>Check platform ownership, processing capacity, delivery channels, latency, connectivity and cloud or edge choices. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G23" s="18" t="str">
-        <x:v>Architecture review; platform ownership; load tests; compute sizing; connectivity assessment.</x:v>
-      </x:c>
-      <x:c r="H23" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I23" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="str">
-        <x:v>2213; 2221</x:v>
-      </x:c>
-      <x:c r="L23" s="18" t="str">
-        <x:v>2213: Gate 4-Steady-State Operation &amp; Evolution; 2221: Gate 2- Solution Build &amp; Verification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="85" customHeight="1">
-      <x:c r="A24" s="18" t="str">
-        <x:v>RQ-1024-01</x:v>
-      </x:c>
-      <x:c r="B24" s="18" t="str">
-        <x:v>Are data quality responsibilities and criteria agreed, and is quality and semantic consistency demonstrated across required systems?</x:v>
-      </x:c>
-      <x:c r="C24" s="18" t="str">
-        <x:v>Organisational; Technical</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E24" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F24" s="18" t="str">
-        <x:v>Check organisational ownership and technical profiling separately. Agree thresholds for this use case and common meaning across sources. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G24" s="18" t="str">
-        <x:v>Data quality policy; ownership matrix; data profiling; semantic dictionary; reconciliation tests.</x:v>
-      </x:c>
-      <x:c r="H24" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I24" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="str">
-        <x:v>1024; 2123</x:v>
-      </x:c>
-      <x:c r="L24" s="18" t="str">
-        <x:v>1024: Gate 2- Solution Build &amp; Verification; 2123: Gate 2- Solution Build &amp; Verification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="85" customHeight="1">
-      <x:c r="A25" s="18" t="str">
-        <x:v>RQ-3114-01</x:v>
-      </x:c>
-      <x:c r="B25" s="18" t="str">
-        <x:v>Is the required data collected, retained and securely available through the target architecture at usable frequency and granularity?</x:v>
-      </x:c>
-      <x:c r="C25" s="18" t="str">
-        <x:v>Cross-cutting; Technical</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E25" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F25" s="18" t="str">
-        <x:v>Demonstrate coverage, retention, access, data movement and enforceable controls. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G25" s="18" t="str">
-        <x:v>Data inventory; retention plan; coverage tests; data flow diagram; access and control tests.</x:v>
-      </x:c>
-      <x:c r="H25" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I25" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="str">
-        <x:v>3114; 2134</x:v>
-      </x:c>
-      <x:c r="L25" s="18" t="str">
-        <x:v>3114: Gate 2- Solution Build &amp; Verification; 2134: Gate 2- Solution Build &amp; Verification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="85" customHeight="1">
-      <x:c r="A26" s="18" t="str">
-        <x:v>RQ-2231-01</x:v>
-      </x:c>
-      <x:c r="B26" s="18" t="str">
-        <x:v>Are software and vendor dependencies maintainable and sufficiently portable?</x:v>
-      </x:c>
-      <x:c r="C26" s="18" t="str">
-        <x:v>Technical</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="str">
-        <x:v>Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-      <x:c r="E26" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F26" s="18" t="str">
-        <x:v>Assess specialist support, exit options and long-term sustainability. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G26" s="18" t="str">
-        <x:v>Dependency inventory; support terms; portability and exit assessment.</x:v>
-      </x:c>
-      <x:c r="H26" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I26" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="str">
-        <x:v>2231</x:v>
-      </x:c>
-      <x:c r="L26" s="18" t="str">
-        <x:v>2231: Gate 4-Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="85" customHeight="1">
-      <x:c r="A27" s="18" t="str">
-        <x:v>RQ-2313-01</x:v>
-      </x:c>
-      <x:c r="B27" s="18" t="str">
-        <x:v>Can AI recommendations flow into enterprise and maintenance workflows, with users able to act and return field feedback?</x:v>
-      </x:c>
-      <x:c r="C27" s="18" t="str">
-        <x:v>Technical; Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E27" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F27" s="18" t="str">
-        <x:v>Verify asset records, work orders, maintenance planning and feedback interfaces end to end. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G27" s="18" t="str">
-        <x:v>Interface specification; integration tests; work-order trial; operator feedback process.</x:v>
-      </x:c>
-      <x:c r="H27" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I27" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="str">
-        <x:v>2313; 3333</x:v>
-      </x:c>
-      <x:c r="L27" s="18" t="str">
-        <x:v>2313: Gate 2- Solution Build &amp; Verification; 3333: Gate 3- Operational Deployment &amp; Commissioning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="85" customHeight="1">
-      <x:c r="A28" s="18" t="str">
-        <x:v>RQ-2323-01</x:v>
-      </x:c>
-      <x:c r="B28" s="18" t="str">
-        <x:v>Are OT, monitoring, alarm procedures and operational workflows integrated reliably?</x:v>
-      </x:c>
-      <x:c r="C28" s="18" t="str">
-        <x:v>Technical</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="str">
-        <x:v>Solution Build &amp; Verification</x:v>
-      </x:c>
-      <x:c r="E28" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F28" s="18" t="str">
-        <x:v>Test relevant live-system interfaces and failure handling. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G28" s="18" t="str">
-        <x:v>OT interface tests; alarm procedure; operational trial evidence.</x:v>
-      </x:c>
-      <x:c r="H28" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I28" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="str">
-        <x:v>2323</x:v>
-      </x:c>
-      <x:c r="L28" s="18" t="str">
-        <x:v>2323: Gate 2- Solution Build &amp; Verification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="85" customHeight="1">
-      <x:c r="A29" s="18" t="str">
-        <x:v>RQ-2423-01</x:v>
-      </x:c>
-      <x:c r="B29" s="18" t="str">
-        <x:v>Are model monitoring, retraining and controlled evolution arrangements in place?</x:v>
-      </x:c>
-      <x:c r="C29" s="18" t="str">
-        <x:v>Technical</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="str">
-        <x:v>Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-      <x:c r="E29" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F29" s="18" t="str">
-        <x:v>Define drift thresholds, response owners and revalidation triggers. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G29" s="18" t="str">
-        <x:v>Monitoring plan; drift tests; retraining and change control records.</x:v>
-      </x:c>
-      <x:c r="H29" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I29" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="str">
-        <x:v>2423</x:v>
-      </x:c>
-      <x:c r="L29" s="18" t="str">
-        <x:v>2423: Gate 4-Steady-State Operation &amp; Evolution</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="85" customHeight="1">
-      <x:c r="A30" s="18" t="str">
-        <x:v>RQ-3123-01</x:v>
-      </x:c>
-      <x:c r="B30" s="18" t="str">
-        <x:v>Have solution approaches been compared against operational and scalability requirements?</x:v>
-      </x:c>
-      <x:c r="C30" s="18" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="str">
-        <x:v>Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-      <x:c r="E30" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F30" s="18" t="str">
-        <x:v>Include alternative technologies and justify the chosen approach. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G30" s="18" t="str">
-        <x:v>Options appraisal; architecture decision record; feasibility assessment.</x:v>
-      </x:c>
-      <x:c r="H30" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I30" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="str">
-        <x:v>3123</x:v>
-      </x:c>
-      <x:c r="L30" s="18" t="str">
-        <x:v>3123: Gate 1-Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="85" customHeight="1">
-      <x:c r="A31" s="18" t="str">
-        <x:v>RQ-3744-01</x:v>
-      </x:c>
-      <x:c r="B31" s="18" t="str">
-        <x:v>Have safety implications and oversight needs been identified, with an agreed assurance plan and evidence for reliability at scale?</x:v>
-      </x:c>
-      <x:c r="C31" s="18" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="str">
-        <x:v>Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-      <x:c r="E31" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F31" s="18" t="str">
-        <x:v>Trace hazards and failure modes into human oversight and assurance evidence requirements. Confirm outstanding evidence with reviewers. Assess every component separately. Record partial readiness, gaps and evidence owners.</x:v>
-      </x:c>
-      <x:c r="G31" s="18" t="str">
-        <x:v>Hazard analysis; oversight design; assurance plan; reliability tests; safety evidence register.</x:v>
-      </x:c>
-      <x:c r="H31" s="18" t="str">
-        <x:v>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</x:v>
-      </x:c>
-      <x:c r="I31" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="str">
-        <x:v>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="str">
-        <x:v>3744; 3734</x:v>
-      </x:c>
-      <x:c r="L31" s="18" t="str">
-        <x:v>3744: Gate 1-Solution Architecture &amp; Feasibility; 3734: Gate 1-Solution Architecture &amp; Feasibility</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="I6:I31">
-      <x:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe11539e17354f10"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Candidate AI project readiness questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Keep assigned question IDs stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Question_ID</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Lifecycle_Stage</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Provisional_Stage_Gate</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Evidence_Examples</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Applicability</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Review_Status</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Review_Comments</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Source_Blocker_IDs</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Source_Stage_Gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1114-01</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Is the project anchored in a validated operational problem, an accountable owner and the shared AI vision?</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Confirm problem evidence, ownership and strategic alignment separately. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Problem baseline; owner approval; AI strategy alignment.</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>1114; 1211</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>1114: Gate 0-Strategic Alignment &amp; Idea Validation; 1211: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="85" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1133-01</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Is the expected value clear to each affected stakeholder group?</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Separate benefits for maintenance, asset management, operations and leadership. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Stakeholder value statements; interviews; benefit measures.</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>1133: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="85" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1143-01</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Does the business case address costs, benefits, risks and funding of shared foundations?</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Distinguish use-case costs from reusable platform, data and governance investments. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Cost model; risk register; shared investment allocation.</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>1143: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="85" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1223-01</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Have cross-functional priorities and competing AI initiatives been reconciled?</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Identify duplicated work and portfolio-level resource conflicts. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Portfolio review; prioritisation decisions; resource commitments.</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>1223: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="85" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1233-01</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Do teams share evidence-based readiness criteria, decision rights and a timely review process?</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Document readiness criteria, reviewers, approval authority and decision deadlines. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Readiness checklist; governance charter; decision matrix; review calendar.</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>1233; 1823</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>1233: Gate 0-Strategic Alignment &amp; Idea Validation; 1823: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="85" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1243-01</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Is management sponsorship and funding sustained through deployment and operation?</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Confirm commitments beyond the pilot and arrangements for recurring reviews. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Sponsor commitments; funding plan; steering review minutes.</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>1243: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="85" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1314-01</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Are business ownership and human accountability defined for operational use beyond the prototype?</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Confirm benefit ownership and responsibilities for judgement, approval, action and escalation. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Ownership agreement; decision workflow; responsibility matrix; escalation procedure.</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>1314; 1323</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>1314: Gate 3- Operational Deployment &amp; Commissioning; 1323: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="85" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1334-01</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Has the production operating model been funded and accepted through a reproducible deployment and support handover?</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Check support ownership, monitoring, incidents, deployment reproducibility and handover acceptance. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Run budget; support acceptance; deployment records; telemetry and recovery tests.</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>1334; 3413</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>1334: Gate 3- Operational Deployment &amp; Commissioning; 3413: Gate 4-Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="85" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1413-01</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Do affected teams have the skills to interpret, challenge and use AI outputs?</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Assess role-specific competence and address training gaps. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Skills assessment; training plan; competence demonstration.</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>1413: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="85" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1424-01</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Have field users demonstrated that they can understand, challenge and use the AI outputs, with adoption concerns addressed?</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Assess interpretation and trust with affected users. Record unresolved concerns and workflow burden. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>User interpretation trials; explanation examples; co-design and adoption feedback.</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>1424; 3523</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>1424: Gate 0-Strategic Alignment &amp; Idea Validation; 3523: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="85" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1433-01</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Can the organisation absorb iterative releases and transition to changed AI capabilities?</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Retirement &amp; Transition</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Assess change capacity across releases and eventual replacement or retirement. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Change capacity assessment; release plan; transition and training plan.</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>Source assigns Gate 5. Review earlier lifecycle applicability. UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>1433: Gate 5-Retirement &amp; Transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="85" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1511-01</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Do decision-makers understand the proposed AI capability, data needs and limitations?</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Test expectations against realistic operational conditions and assurance needs. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Capability briefing; limitations register; feasibility evidence.</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>1511: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="85" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1524-01</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Does the proposed solution fit real railway field conditions and support needs?</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Consider possession windows, connectivity, shifts and maintenance practices. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Field workflow observations; operational requirements; support assessment.</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>1524: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1614-01</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Are cross-unit data ownership, access rules and sharing arrangements usable for reuse beyond the local pilot?</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Confirm governance and practical access across silos, including interoperability and control responsibilities. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Data sharing agreements; access approvals; cross-unit reuse trial; governance decision records.</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>1614; 3634</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>1614: Gate 0-Strategic Alignment &amp; Idea Validation; 3634: Gate 0-Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1713-01</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Has a suitably informed legal team assessed applicable requirements and unresolved regulatory interpretations?</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Organisational</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Confirm specialist capability, document interpretations and assign owners to unresolved questions. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Legal assessment; specialist input; requirements register; unresolved issue log.</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>1713; 1723</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>1713: Gate 1-Solution Architecture &amp; Feasibility; 1723: Gate 1-Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="85" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1811-01</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Is the intended scale defined, and is model performance demonstrated across that scope and operational variation?</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Technical</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Define sites, assets, users and workloads, then test false positives, missed detections and segment performance. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Scaling scope; volume assumptions; segment validation results; acceptance thresholds.</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>1811; 2513</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>1811: Gate 2- Solution Build &amp; Verification; 2513: Gate 4-Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="85" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1043-01</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Is there a realistic incremental pathway from MVP and PoC to production, with owners and evidence at each milestone?</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Technical</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Strategic Alignment &amp; Idea Validation</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Assess increments, transition work, integration and assurance dependencies, resources and approval lead times. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>MVP roadmap; production transition plan; integrated schedule; field validation milestones.</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>1043; 1833; 1921</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>1043: Gate 0-Strategic Alignment &amp; Idea Validation; 1833: Gate 0-Strategic Alignment &amp; Idea Validation; 1921: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="85" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2213-01</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Can the governed platform and compute environment sustain the intended workload and operational constraints?</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Check platform ownership, processing capacity, delivery channels, latency, connectivity and cloud or edge choices. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>Architecture review; platform ownership; load tests; compute sizing; connectivity assessment.</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>2213; 2221</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>2213: Gate 4-Steady-State Operation &amp; Evolution; 2221: Gate 2- Solution Build &amp; Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1024-01</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Are data quality responsibilities and criteria agreed, and is quality and semantic consistency demonstrated across required systems?</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Organisational; Technical</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Check organisational ownership and technical profiling separately. Agree thresholds for this use case and common meaning across sources. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Data quality policy; ownership matrix; data profiling; semantic dictionary; reconciliation tests.</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>1024; 2123</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>1024: Gate 2- Solution Build &amp; Verification; 2123: Gate 2- Solution Build &amp; Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="85" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3114-01</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Is the required data collected, retained and securely available through the target architecture at usable frequency and granularity?</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Cross-cutting; Technical</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Demonstrate coverage, retention, access, data movement and enforceable controls. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Data inventory; retention plan; coverage tests; data flow diagram; access and control tests.</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>3114; 2134</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>3114: Gate 2- Solution Build &amp; Verification; 2134: Gate 2- Solution Build &amp; Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="85" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2231-01</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Are software and vendor dependencies maintainable and sufficiently portable?</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Assess specialist support, exit options and long-term sustainability. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Dependency inventory; support terms; portability and exit assessment.</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>2231: Gate 4-Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="85" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2313-01</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Can AI recommendations flow into enterprise and maintenance workflows, with users able to act and return field feedback?</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Technical; Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Verify asset records, work orders, maintenance planning and feedback interfaces end to end. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Interface specification; integration tests; work-order trial; operator feedback process.</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Multiple source gates: proposed earliest review, revisit at later mapped gates. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>2313; 3333</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>2313: Gate 2- Solution Build &amp; Verification; 3333: Gate 3- Operational Deployment &amp; Commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="85" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2323-01</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Are OT, monitoring, alarm procedures and operational workflows integrated reliably?</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Solution Build &amp; Verification</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Test relevant live-system interfaces and failure handling. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>OT interface tests; alarm procedure; operational trial evidence.</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>2323: Gate 2- Solution Build &amp; Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="85" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2423-01</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Are model monitoring, retraining and controlled evolution arrangements in place?</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Define drift thresholds, response owners and revalidation triggers. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Monitoring plan; drift tests; retraining and change control records.</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>2423: Gate 4-Steady-State Operation &amp; Evolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="85" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3123-01</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Have solution approaches been compared against operational and scalability requirements?</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Include alternative technologies and justify the chosen approach. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Options appraisal; architecture decision record; feasibility assessment.</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>3123: Gate 1-Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="85" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3744-01</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Have safety implications and oversight needs been identified, with an agreed assurance plan and evidence for reliability at scale?</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Trace hazards and failure modes into human oversight and assurance evidence requirements. Confirm outstanding evidence with reviewers. Assess every component separately. Record partial readiness, gaps and evidence owners.</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>Hazard analysis; oversight design; assurance plan; reliability tests; safety evidence register.</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>Candidate for railway AI projects. UIC must confirm scope; assessors may mark N/A with a reason.</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>UIC must review wording, scope and evidence. Source gate retained provisionally. A positive answer does not clear every mapped blocker.</t>
+        </is>
+      </c>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>3744; 3734</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>3744: Gate 1-Solution Architecture &amp; Feasibility; 3734: Gate 1-Solution Architecture &amp; Feasibility</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I6:I31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="65" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="21" t="str">
-        <x:v>Candidate question-to-blocker mappings</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="16" t="str">
-        <x:v>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="16" t="str">
-        <x:v>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Stable keys use numeric blocker IDs; do not renumber after sorting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="20" t="str">
-        <x:v>Question_ID</x:v>
-      </x:c>
-      <x:c r="B5" s="20" t="str">
-        <x:v>Blocker_ID</x:v>
-      </x:c>
-      <x:c r="C5" s="20" t="str">
-        <x:v>Blocker_Code</x:v>
-      </x:c>
-      <x:c r="D5" s="20" t="str">
-        <x:v>Blocker_Title</x:v>
-      </x:c>
-      <x:c r="E5" s="20" t="str">
-        <x:v>Relationship</x:v>
-      </x:c>
-      <x:c r="F5" s="20" t="str">
-        <x:v>Rationale</x:v>
-      </x:c>
-      <x:c r="G5" s="20" t="str">
-        <x:v>Review_Status</x:v>
-      </x:c>
-      <x:c r="H5" s="20" t="str">
-        <x:v>Review_Comments</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="65" customHeight="1">
-      <x:c r="A6" s="18" t="str">
-        <x:v>RQ-1114-01</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="n">
-        <x:v>1114</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>B-01</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>Technology-push AI initiatives without clear ownership</x:v>
-      </x:c>
-      <x:c r="E6" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="str">
-        <x:v>Question explicitly assesses Technology-push AI initiatives without clear ownership. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G6" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H6" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="65" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>RQ-1114-01</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="n">
-        <x:v>1211</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>B-04</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Lack of shared AI vision</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>Question explicitly assesses Lack of shared AI vision. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H7" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="65" customHeight="1">
-      <x:c r="A8" s="18" t="str">
-        <x:v>RQ-1133-01</x:v>
-      </x:c>
-      <x:c r="B8" s="18" t="n">
-        <x:v>1133</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>B-02</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>Unclear value articulation for stakeholder groups</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F8" s="18" t="str">
-        <x:v>Question explicitly assesses Unclear value articulation for stakeholder groups. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G8" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H8" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="65" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>RQ-1143-01</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="n">
-        <x:v>1143</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>B-03</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Unclear financial implications, risks and investment logic</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
-        <x:v>Question explicitly assesses Unclear financial implications, risks and investment logic. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="65" customHeight="1">
-      <x:c r="A10" s="18" t="str">
-        <x:v>RQ-1223-01</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="n">
-        <x:v>1223</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>B-05</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="str">
-        <x:v>Fragmented AI priorities across silos</x:v>
-      </x:c>
-      <x:c r="E10" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F10" s="18" t="str">
-        <x:v>Question explicitly assesses Fragmented AI priorities across silos. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G10" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H10" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="65" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>RQ-1233-01</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="n">
-        <x:v>1233</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>B-06</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Slow or unclear AI governance</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="str">
-        <x:v>Question explicitly assesses Slow or unclear AI governance. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H11" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="65" customHeight="1">
-      <x:c r="A12" s="18" t="str">
-        <x:v>RQ-1233-01</x:v>
-      </x:c>
-      <x:c r="B12" s="18" t="n">
-        <x:v>1823</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="str">
-        <x:v>B-23</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="str">
-        <x:v>There is no shared understanding of AI project maturity and readiness across teams and decision-makers.</x:v>
-      </x:c>
-      <x:c r="E12" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F12" s="18" t="str">
-        <x:v>Question explicitly assesses There is no shared understanding of AI project maturity and readiness across teams and decision-makers.. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G12" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H12" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="65" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>RQ-1243-01</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="n">
-        <x:v>1243</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>B-07</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Insufficient sustained management commitment 'towards the end goal'</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F13" s="18" t="str">
-        <x:v>Question explicitly assesses Insufficient sustained management commitment 'towards the end goal'. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G13" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H13" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="65" customHeight="1">
-      <x:c r="A14" s="18" t="str">
-        <x:v>RQ-1314-01</x:v>
-      </x:c>
-      <x:c r="B14" s="18" t="n">
-        <x:v>1314</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>B-08</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="str">
-        <x:v>No business ownership beyond prototype</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="str">
-        <x:v>Question explicitly assesses No business ownership beyond prototype. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H14" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="65" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>RQ-1314-01</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="n">
-        <x:v>1323</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>B-09</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Unclear human accountability in AI-supported operational decisions</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str">
-        <x:v>Question explicitly assesses Unclear human accountability in AI-supported operational decisions. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G15" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H15" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="65" customHeight="1">
-      <x:c r="A16" s="18" t="str">
-        <x:v>RQ-1334-01</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="n">
-        <x:v>1334</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="str">
-        <x:v>B-10</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="str">
-        <x:v>No defined run model after go-live</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="str">
-        <x:v>Question explicitly assesses No defined run model after go-live. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G16" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H16" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="65" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>RQ-1334-01</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="n">
-        <x:v>3413</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>B-34</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
-        <x:v>Production-grade AI operations and handover gap</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F17" s="18" t="str">
-        <x:v>Question explicitly assesses Production-grade AI operations and handover gap. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G17" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H17" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="65" customHeight="1">
-      <x:c r="A18" s="18" t="str">
-        <x:v>RQ-1413-01</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="n">
-        <x:v>1413</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="str">
-        <x:v>B-11</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="str">
-        <x:v>Insufficient AI and digital skills across the organisation</x:v>
-      </x:c>
-      <x:c r="E18" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F18" s="18" t="str">
-        <x:v>Question explicitly assesses Insufficient AI and digital skills across the organisation. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G18" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H18" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="65" customHeight="1">
-      <x:c r="A19" s="18" t="str">
-        <x:v>RQ-1424-01</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="n">
-        <x:v>1424</x:v>
-      </x:c>
-      <x:c r="C19" s="18" t="str">
-        <x:v>B-12</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="str">
-        <x:v>Low trust and cultural resistance to AI</x:v>
-      </x:c>
-      <x:c r="E19" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="str">
-        <x:v>Question explicitly assesses Low trust and cultural resistance to AI. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G19" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H19" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="65" customHeight="1">
-      <x:c r="A20" s="18" t="str">
-        <x:v>RQ-1424-01</x:v>
-      </x:c>
-      <x:c r="B20" s="18" t="n">
-        <x:v>3523</x:v>
-      </x:c>
-      <x:c r="C20" s="18" t="str">
-        <x:v>B-37</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="str">
-        <x:v>Limited explainability, interpretability and field trust</x:v>
-      </x:c>
-      <x:c r="E20" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F20" s="18" t="str">
-        <x:v>Question explicitly assesses Limited explainability, interpretability and field trust. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G20" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H20" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="65" customHeight="1">
-      <x:c r="A21" s="18" t="str">
-        <x:v>RQ-1433-01</x:v>
-      </x:c>
-      <x:c r="B21" s="18" t="n">
-        <x:v>1433</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="str">
-        <x:v>B-13</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="str">
-        <x:v>Limited capacity to absorb continuous change</x:v>
-      </x:c>
-      <x:c r="E21" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F21" s="18" t="str">
-        <x:v>Question explicitly assesses Limited capacity to absorb continuous change. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G21" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H21" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="65" customHeight="1">
-      <x:c r="A22" s="18" t="str">
-        <x:v>RQ-1511-01</x:v>
-      </x:c>
-      <x:c r="B22" s="18" t="n">
-        <x:v>1511</x:v>
-      </x:c>
-      <x:c r="C22" s="18" t="str">
-        <x:v>B-14</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="str">
-        <x:v>Unrealistic understanding of AI capabilities and limits among decision-makers</x:v>
-      </x:c>
-      <x:c r="E22" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F22" s="18" t="str">
-        <x:v>Question explicitly assesses Unrealistic understanding of AI capabilities and limits among decision-makers. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G22" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H22" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="65" customHeight="1">
-      <x:c r="A23" s="18" t="str">
-        <x:v>RQ-1524-01</x:v>
-      </x:c>
-      <x:c r="B23" s="18" t="n">
-        <x:v>1524</x:v>
-      </x:c>
-      <x:c r="C23" s="18" t="str">
-        <x:v>B-15</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="str">
-        <x:v>Solutions misaligned with operational context</x:v>
-      </x:c>
-      <x:c r="E23" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F23" s="18" t="str">
-        <x:v>Question explicitly assesses Solutions misaligned with operational context. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G23" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H23" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="65" customHeight="1">
-      <x:c r="A24" s="18" t="str">
-        <x:v>RQ-1614-01</x:v>
-      </x:c>
-      <x:c r="B24" s="18" t="n">
-        <x:v>1614</x:v>
-      </x:c>
-      <x:c r="C24" s="18" t="str">
-        <x:v>B-16</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="str">
-        <x:v>Fragmented or restrictive data governance</x:v>
-      </x:c>
-      <x:c r="E24" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F24" s="18" t="str">
-        <x:v>Question explicitly assesses Fragmented or restrictive data governance. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G24" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H24" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="65" customHeight="1">
-      <x:c r="A25" s="18" t="str">
-        <x:v>RQ-1614-01</x:v>
-      </x:c>
-      <x:c r="B25" s="18" t="n">
-        <x:v>3634</x:v>
-      </x:c>
-      <x:c r="C25" s="18" t="str">
-        <x:v>B-18</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="str">
-        <x:v>Organisational data silos limiting reuse and scaling</x:v>
-      </x:c>
-      <x:c r="E25" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F25" s="18" t="str">
-        <x:v>Question explicitly assesses Organisational data silos limiting reuse and scaling. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G25" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H25" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="65" customHeight="1">
-      <x:c r="A26" s="18" t="str">
-        <x:v>RQ-1713-01</x:v>
-      </x:c>
-      <x:c r="B26" s="18" t="n">
-        <x:v>1713</x:v>
-      </x:c>
-      <x:c r="C26" s="18" t="str">
-        <x:v>B-19</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="str">
-        <x:v>Limited AI expertise in legal functions</x:v>
-      </x:c>
-      <x:c r="E26" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F26" s="18" t="str">
-        <x:v>Question explicitly assesses Limited AI expertise in legal functions. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G26" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H26" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="65" customHeight="1">
-      <x:c r="A27" s="18" t="str">
-        <x:v>RQ-1713-01</x:v>
-      </x:c>
-      <x:c r="B27" s="18" t="n">
-        <x:v>1723</x:v>
-      </x:c>
-      <x:c r="C27" s="18" t="str">
-        <x:v>B-20</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="str">
-        <x:v>Unclear regulatory interpretation increases perceived risk</x:v>
-      </x:c>
-      <x:c r="E27" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F27" s="18" t="str">
-        <x:v>Question explicitly assesses Unclear regulatory interpretation increases perceived risk. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G27" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H27" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="65" customHeight="1">
-      <x:c r="A28" s="18" t="str">
-        <x:v>RQ-1811-01</x:v>
-      </x:c>
-      <x:c r="B28" s="18" t="n">
-        <x:v>1811</x:v>
-      </x:c>
-      <x:c r="C28" s="18" t="str">
-        <x:v>B-22</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="str">
-        <x:v>Ambiguous definition of scaling</x:v>
-      </x:c>
-      <x:c r="E28" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F28" s="18" t="str">
-        <x:v>Question explicitly assesses Ambiguous definition of scaling. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G28" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H28" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="65" customHeight="1">
-      <x:c r="A29" s="18" t="str">
-        <x:v>RQ-1811-01</x:v>
-      </x:c>
-      <x:c r="B29" s="18" t="n">
-        <x:v>2513</x:v>
-      </x:c>
-      <x:c r="C29" s="18" t="str">
-        <x:v>B-36</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="str">
-        <x:v>Model performance degrades with scale</x:v>
-      </x:c>
-      <x:c r="E29" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F29" s="18" t="str">
-        <x:v>Question explicitly assesses Model performance degrades with scale. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G29" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H29" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="65" customHeight="1">
-      <x:c r="A30" s="18" t="str">
-        <x:v>RQ-1043-01</x:v>
-      </x:c>
-      <x:c r="B30" s="18" t="n">
-        <x:v>1043</x:v>
-      </x:c>
-      <x:c r="C30" s="18" t="str">
-        <x:v>B-40</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="str">
-        <x:v>Weak MVP and incremental delivery discipline</x:v>
-      </x:c>
-      <x:c r="E30" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F30" s="18" t="str">
-        <x:v>Question explicitly assesses Weak MVP and incremental delivery discipline. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G30" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H30" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="65" customHeight="1">
-      <x:c r="A31" s="18" t="str">
-        <x:v>RQ-1043-01</x:v>
-      </x:c>
-      <x:c r="B31" s="18" t="n">
-        <x:v>1833</x:v>
-      </x:c>
-      <x:c r="C31" s="18" t="str">
-        <x:v>B-24</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="str">
-        <x:v>PoC to production transition stalls</x:v>
-      </x:c>
-      <x:c r="E31" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F31" s="18" t="str">
-        <x:v>Question explicitly assesses PoC to production transition stalls. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G31" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H31" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="65" customHeight="1">
-      <x:c r="A32" s="18" t="str">
-        <x:v>RQ-1043-01</x:v>
-      </x:c>
-      <x:c r="B32" s="18" t="n">
-        <x:v>1921</x:v>
-      </x:c>
-      <x:c r="C32" s="18" t="str">
-        <x:v>B-42</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="str">
-        <x:v>Unrealistic delivery timelines and scaling ambition</x:v>
-      </x:c>
-      <x:c r="E32" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F32" s="18" t="str">
-        <x:v>Question explicitly assesses Unrealistic delivery timelines and scaling ambition. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G32" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H32" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="65" customHeight="1">
-      <x:c r="A33" s="18" t="str">
-        <x:v>RQ-2213-01</x:v>
-      </x:c>
-      <x:c r="B33" s="18" t="n">
-        <x:v>2213</x:v>
-      </x:c>
-      <x:c r="C33" s="18" t="str">
-        <x:v>B-28</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="str">
-        <x:v>Immature platform architecture and fragmented IT foundations</x:v>
-      </x:c>
-      <x:c r="E33" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F33" s="18" t="str">
-        <x:v>Question explicitly assesses Immature platform architecture and fragmented IT foundations. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G33" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H33" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="65" customHeight="1">
-      <x:c r="A34" s="18" t="str">
-        <x:v>RQ-2213-01</x:v>
-      </x:c>
-      <x:c r="B34" s="18" t="n">
-        <x:v>2221</x:v>
-      </x:c>
-      <x:c r="C34" s="18" t="str">
-        <x:v>B-29</x:v>
-      </x:c>
-      <x:c r="D34" s="18" t="str">
-        <x:v>Compute environment constraints for AI deployment</x:v>
-      </x:c>
-      <x:c r="E34" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F34" s="18" t="str">
-        <x:v>Question explicitly assesses Compute environment constraints for AI deployment. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G34" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H34" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="65" customHeight="1">
-      <x:c r="A35" s="18" t="str">
-        <x:v>RQ-1024-01</x:v>
-      </x:c>
-      <x:c r="B35" s="18" t="n">
-        <x:v>1024</x:v>
-      </x:c>
-      <x:c r="C35" s="18" t="str">
-        <x:v>B-39</x:v>
-      </x:c>
-      <x:c r="D35" s="18" t="str">
-        <x:v>Inconsistent data quality management across AI use cases</x:v>
-      </x:c>
-      <x:c r="E35" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F35" s="18" t="str">
-        <x:v>Question explicitly assesses Inconsistent data quality management across AI use cases. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G35" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H35" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="65" customHeight="1">
-      <x:c r="A36" s="18" t="str">
-        <x:v>RQ-1024-01</x:v>
-      </x:c>
-      <x:c r="B36" s="18" t="n">
-        <x:v>2123</x:v>
-      </x:c>
-      <x:c r="C36" s="18" t="str">
-        <x:v>B-26</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="str">
-        <x:v>Data quality, consistency and semantic structure</x:v>
-      </x:c>
-      <x:c r="E36" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F36" s="18" t="str">
-        <x:v>Question explicitly assesses Data quality, consistency and semantic structure. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G36" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H36" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="65" customHeight="1">
-      <x:c r="A37" s="18" t="str">
-        <x:v>RQ-3114-01</x:v>
-      </x:c>
-      <x:c r="B37" s="18" t="n">
-        <x:v>3114</x:v>
-      </x:c>
-      <x:c r="C37" s="18" t="str">
-        <x:v>B-25</x:v>
-      </x:c>
-      <x:c r="D37" s="18" t="str">
-        <x:v>Data collection, storage and usable availability</x:v>
-      </x:c>
-      <x:c r="E37" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F37" s="18" t="str">
-        <x:v>Question explicitly assesses Data collection, storage and usable availability. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G37" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H37" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="65" customHeight="1">
-      <x:c r="A38" s="18" t="str">
-        <x:v>RQ-3114-01</x:v>
-      </x:c>
-      <x:c r="B38" s="18" t="n">
-        <x:v>2134</x:v>
-      </x:c>
-      <x:c r="C38" s="18" t="str">
-        <x:v>B-27</x:v>
-      </x:c>
-      <x:c r="D38" s="18" t="str">
-        <x:v>Data architecture, access and controls</x:v>
-      </x:c>
-      <x:c r="E38" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F38" s="18" t="str">
-        <x:v>Question explicitly assesses Data architecture, access and controls. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G38" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H38" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="65" customHeight="1">
-      <x:c r="A39" s="18" t="str">
-        <x:v>RQ-2231-01</x:v>
-      </x:c>
-      <x:c r="B39" s="18" t="n">
-        <x:v>2231</x:v>
-      </x:c>
-      <x:c r="C39" s="18" t="str">
-        <x:v>B-30</x:v>
-      </x:c>
-      <x:c r="D39" s="18" t="str">
-        <x:v>Software stack, tooling and vendor dependency constraints</x:v>
-      </x:c>
-      <x:c r="E39" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F39" s="18" t="str">
-        <x:v>Question explicitly assesses Software stack, tooling and vendor dependency constraints. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G39" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H39" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="65" customHeight="1">
-      <x:c r="A40" s="18" t="str">
-        <x:v>RQ-2313-01</x:v>
-      </x:c>
-      <x:c r="B40" s="18" t="n">
-        <x:v>2313</x:v>
-      </x:c>
-      <x:c r="C40" s="18" t="str">
-        <x:v>B-31</x:v>
-      </x:c>
-      <x:c r="D40" s="18" t="str">
-        <x:v>Enterprise and asset management system integration</x:v>
-      </x:c>
-      <x:c r="E40" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F40" s="18" t="str">
-        <x:v>Question explicitly assesses Enterprise and asset management system integration. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G40" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H40" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="65" customHeight="1">
-      <x:c r="A41" s="18" t="str">
-        <x:v>RQ-2313-01</x:v>
-      </x:c>
-      <x:c r="B41" s="18" t="n">
-        <x:v>3333</x:v>
-      </x:c>
-      <x:c r="C41" s="18" t="str">
-        <x:v>B-33</x:v>
-      </x:c>
-      <x:c r="D41" s="18" t="str">
-        <x:v>Maintenance workflow integration and operator feedback loops</x:v>
-      </x:c>
-      <x:c r="E41" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F41" s="18" t="str">
-        <x:v>Question explicitly assesses Maintenance workflow integration and operator feedback loops. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G41" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H41" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="65" customHeight="1">
-      <x:c r="A42" s="18" t="str">
-        <x:v>RQ-2323-01</x:v>
-      </x:c>
-      <x:c r="B42" s="18" t="n">
-        <x:v>2323</x:v>
-      </x:c>
-      <x:c r="C42" s="18" t="str">
-        <x:v>B-32</x:v>
-      </x:c>
-      <x:c r="D42" s="18" t="str">
-        <x:v>OT, monitoring systems and railway operations integration</x:v>
-      </x:c>
-      <x:c r="E42" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F42" s="18" t="str">
-        <x:v>Question explicitly assesses OT, monitoring systems and railway operations integration. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G42" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H42" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="65" customHeight="1">
-      <x:c r="A43" s="18" t="str">
-        <x:v>RQ-2423-01</x:v>
-      </x:c>
-      <x:c r="B43" s="18" t="n">
-        <x:v>2423</x:v>
-      </x:c>
-      <x:c r="C43" s="18" t="str">
-        <x:v>B-35</x:v>
-      </x:c>
-      <x:c r="D43" s="18" t="str">
-        <x:v>Unsufficient Model monitoring, -retraining and -evolution</x:v>
-      </x:c>
-      <x:c r="E43" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F43" s="18" t="str">
-        <x:v>Question explicitly assesses Unsufficient Model monitoring, -retraining and -evolution. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G43" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H43" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="65" customHeight="1">
-      <x:c r="A44" s="18" t="str">
-        <x:v>RQ-3123-01</x:v>
-      </x:c>
-      <x:c r="B44" s="18" t="n">
-        <x:v>3123</x:v>
-      </x:c>
-      <x:c r="C44" s="18" t="str">
-        <x:v>B-44</x:v>
-      </x:c>
-      <x:c r="D44" s="18" t="str">
-        <x:v>Poor solution framing and technology selection</x:v>
-      </x:c>
-      <x:c r="E44" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F44" s="18" t="str">
-        <x:v>Question explicitly assesses Poor solution framing and technology selection. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G44" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H44" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="65" customHeight="1">
-      <x:c r="A45" s="18" t="str">
-        <x:v>RQ-3744-01</x:v>
-      </x:c>
-      <x:c r="B45" s="18" t="n">
-        <x:v>3744</x:v>
-      </x:c>
-      <x:c r="C45" s="18" t="str">
-        <x:v>B-21</x:v>
-      </x:c>
-      <x:c r="D45" s="18" t="str">
-        <x:v>Safety implications not identified early</x:v>
-      </x:c>
-      <x:c r="E45" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F45" s="18" t="str">
-        <x:v>Question explicitly assesses Safety implications not identified early. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G45" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H45" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="65" customHeight="1">
-      <x:c r="A46" s="18" t="str">
-        <x:v>RQ-3744-01</x:v>
-      </x:c>
-      <x:c r="B46" s="18" t="n">
-        <x:v>3734</x:v>
-      </x:c>
-      <x:c r="C46" s="18"/>
-      <x:c r="D46" s="18" t="str">
-        <x:v>Difficulty proving safety and reliability at scale</x:v>
-      </x:c>
-      <x:c r="E46" s="18" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="F46" s="18" t="str">
-        <x:v>Question explicitly assesses Difficulty proving safety and reliability at scale. Evaluate its evidence separately within the grouped question.</x:v>
-      </x:c>
-      <x:c r="G46" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H46" s="18" t="str">
-        <x:v>Draft semantic mapping. UIC validation is required. Source blocker has no code; numeric ID is authoritative.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="65" customHeight="1">
-      <x:c r="A47" s="18" t="str">
-        <x:v>RQ-1114-01</x:v>
-      </x:c>
-      <x:c r="B47" s="18" t="n">
-        <x:v>1314</x:v>
-      </x:c>
-      <x:c r="C47" s="18" t="str">
-        <x:v>B-08</x:v>
-      </x:c>
-      <x:c r="D47" s="18" t="str">
-        <x:v>No business ownership beyond prototype</x:v>
-      </x:c>
-      <x:c r="E47" s="18" t="str">
-        <x:v>Contextual</x:v>
-      </x:c>
-      <x:c r="F47" s="18" t="str">
-        <x:v>Early accountable ownership informs continued ownership beyond the prototype.</x:v>
-      </x:c>
-      <x:c r="G47" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H47" s="18" t="str">
-        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="65" customHeight="1">
-      <x:c r="A48" s="18" t="str">
-        <x:v>RQ-1334-01</x:v>
-      </x:c>
-      <x:c r="B48" s="18" t="n">
-        <x:v>2423</x:v>
-      </x:c>
-      <x:c r="C48" s="18" t="str">
-        <x:v>B-35</x:v>
-      </x:c>
-      <x:c r="D48" s="18" t="str">
-        <x:v>Unsufficient Model monitoring, -retraining and -evolution</x:v>
-      </x:c>
-      <x:c r="E48" s="18" t="str">
-        <x:v>Contextual</x:v>
-      </x:c>
-      <x:c r="F48" s="18" t="str">
-        <x:v>The operating model provides context for ongoing model monitoring.</x:v>
-      </x:c>
-      <x:c r="G48" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H48" s="18" t="str">
-        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="65" customHeight="1">
-      <x:c r="A49" s="18" t="str">
-        <x:v>RQ-1424-01</x:v>
-      </x:c>
-      <x:c r="B49" s="18" t="n">
-        <x:v>1413</x:v>
-      </x:c>
-      <x:c r="C49" s="18" t="str">
-        <x:v>B-11</x:v>
-      </x:c>
-      <x:c r="D49" s="18" t="str">
-        <x:v>Insufficient AI and digital skills across the organisation</x:v>
-      </x:c>
-      <x:c r="E49" s="18" t="str">
-        <x:v>Contextual</x:v>
-      </x:c>
-      <x:c r="F49" s="18" t="str">
-        <x:v>Interpretation and adoption trials may reveal skills needs.</x:v>
-      </x:c>
-      <x:c r="G49" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H49" s="18" t="str">
-        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="65" customHeight="1">
-      <x:c r="A50" s="18" t="str">
-        <x:v>RQ-3114-01</x:v>
-      </x:c>
-      <x:c r="B50" s="18" t="n">
-        <x:v>1024</x:v>
-      </x:c>
-      <x:c r="C50" s="18" t="str">
-        <x:v>B-39</x:v>
-      </x:c>
-      <x:c r="D50" s="18" t="str">
-        <x:v>Inconsistent data quality management across AI use cases</x:v>
-      </x:c>
-      <x:c r="E50" s="18" t="str">
-        <x:v>Contextual</x:v>
-      </x:c>
-      <x:c r="F50" s="18" t="str">
-        <x:v>Data availability provides context for agreed quality responsibilities and criteria.</x:v>
-      </x:c>
-      <x:c r="G50" s="18" t="str">
-        <x:v>Draft - UIC review</x:v>
-      </x:c>
-      <x:c r="H50" s="18" t="str">
-        <x:v>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="G6:G50">
-      <x:formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="E6:E50">
-      <x:formula1>"Direct,Contextual"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700b112c5def4a84"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Candidate question-to-blocker mappings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All content is draft for UIC review. Gate assignments and mappings are provisional, not validated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: supplied Final_Blockers&amp;Enablers_Explorer (5).xlsx, Blockers. Keep assigned question IDs stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Question_ID</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Blocker_ID</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Blocker_Code</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Blocker_Title</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Review_Status</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Review_Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1114-01</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>1114</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Technology-push AI initiatives without clear ownership</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Technology-push AI initiatives without clear ownership. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1114-01</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Lack of shared AI vision</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Lack of shared AI vision. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1133-01</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>1133</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Unclear value articulation for stakeholder groups</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unclear value articulation for stakeholder groups. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1143-01</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1143</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Unclear financial implications, risks and investment logic</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unclear financial implications, risks and investment logic. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1223-01</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>1223</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Fragmented AI priorities across silos</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Fragmented AI priorities across silos. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1233-01</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Slow or unclear AI governance</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Slow or unclear AI governance. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1233-01</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>1823</v>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>B-23</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>There is no shared understanding of AI project maturity and readiness across teams and decision-makers.</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses There is no shared understanding of AI project maturity and readiness across teams and decision-makers.. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1243-01</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>1243</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Insufficient sustained management commitment 'towards the end goal'</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Insufficient sustained management commitment 'towards the end goal'. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1314-01</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>No business ownership beyond prototype</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses No business ownership beyond prototype. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1314-01</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1323</v>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>B-09</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Unclear human accountability in AI-supported operational decisions</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unclear human accountability in AI-supported operational decisions. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1334-01</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>1334</v>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>No defined run model after go-live</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses No defined run model after go-live. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1334-01</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>3413</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>B-34</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Production-grade AI operations and handover gap</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Production-grade AI operations and handover gap. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1413-01</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>1413</v>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Insufficient AI and digital skills across the organisation</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Insufficient AI and digital skills across the organisation. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1424-01</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>1424</v>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Low trust and cultural resistance to AI</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Low trust and cultural resistance to AI. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1424-01</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>3523</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>B-37</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Limited explainability, interpretability and field trust</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Limited explainability, interpretability and field trust. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1433-01</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>1433</v>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>B-13</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Limited capacity to absorb continuous change</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Limited capacity to absorb continuous change. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1511-01</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>1511</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>B-14</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Unrealistic understanding of AI capabilities and limits among decision-makers</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unrealistic understanding of AI capabilities and limits among decision-makers. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1524-01</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>1524</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>B-15</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Solutions misaligned with operational context</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Solutions misaligned with operational context. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="65" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1614-01</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>1614</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>B-16</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Fragmented or restrictive data governance</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Fragmented or restrictive data governance. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1614-01</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>3634</v>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Organisational data silos limiting reuse and scaling</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Organisational data silos limiting reuse and scaling. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1713-01</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>1713</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>B-19</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Limited AI expertise in legal functions</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Limited AI expertise in legal functions. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1713-01</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>B-20</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Unclear regulatory interpretation increases perceived risk</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unclear regulatory interpretation increases perceived risk. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1811-01</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>1811</v>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>B-22</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Ambiguous definition of scaling</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Ambiguous definition of scaling. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1811-01</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>2513</v>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>B-36</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Model performance degrades with scale</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Model performance degrades with scale. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1043-01</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>1043</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>B-40</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Weak MVP and incremental delivery discipline</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Weak MVP and incremental delivery discipline. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1043-01</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>1833</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>B-24</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>PoC to production transition stalls</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses PoC to production transition stalls. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="65" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1043-01</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1921</v>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>B-42</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Unrealistic delivery timelines and scaling ambition</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unrealistic delivery timelines and scaling ambition. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2213-01</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>2213</v>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>B-28</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Immature platform architecture and fragmented IT foundations</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Immature platform architecture and fragmented IT foundations. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="65" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2213-01</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>2221</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>B-29</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Compute environment constraints for AI deployment</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Compute environment constraints for AI deployment. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1024-01</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>B-39</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Inconsistent data quality management across AI use cases</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Inconsistent data quality management across AI use cases. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="65" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1024-01</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>2123</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>B-26</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Data quality, consistency and semantic structure</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Data quality, consistency and semantic structure. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="65" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3114-01</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>3114</v>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>B-25</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>Data collection, storage and usable availability</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Data collection, storage and usable availability. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="65" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3114-01</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>2134</v>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>B-27</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>Data architecture, access and controls</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Data architecture, access and controls. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2231-01</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>2231</v>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>B-30</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Software stack, tooling and vendor dependency constraints</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Software stack, tooling and vendor dependency constraints. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="65" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2313-01</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>2313</v>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>B-31</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Enterprise and asset management system integration</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Enterprise and asset management system integration. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2313-01</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n">
+        <v>3333</v>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>B-33</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Maintenance workflow integration and operator feedback loops</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Maintenance workflow integration and operator feedback loops. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="65" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2323-01</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>2323</v>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>B-32</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>OT, monitoring systems and railway operations integration</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses OT, monitoring systems and railway operations integration. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>RQ-2423-01</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>B-35</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Unsufficient Model monitoring, -retraining and -evolution</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Unsufficient Model monitoring, -retraining and -evolution. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="65" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3123-01</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>3123</v>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>B-44</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Poor solution framing and technology selection</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Poor solution framing and technology selection. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3744-01</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>3744</v>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>B-21</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Safety implications not identified early</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Safety implications not identified early. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="65" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3744-01</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>3734</v>
+      </c>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Difficulty proving safety and reliability at scale</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Question explicitly assesses Difficulty proving safety and reliability at scale. Evaluate its evidence separately within the grouped question.</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Draft semantic mapping. UIC validation is required. Source blocker has no code; numeric ID is authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1114-01</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>No business ownership beyond prototype</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>Contextual</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Early accountable ownership informs continued ownership beyond the prototype.</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="65" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1334-01</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>B-35</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Unsufficient Model monitoring, -retraining and -evolution</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>Contextual</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>The operating model provides context for ongoing model monitoring.</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>RQ-1424-01</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>1413</v>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Insufficient AI and digital skills across the organisation</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>Contextual</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Interpretation and adoption trials may reveal skills needs.</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="65" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>RQ-3114-01</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>B-39</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Inconsistent data quality management across AI use cases</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>Contextual</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Data availability provides context for agreed quality responsibilities and criteria.</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Draft - UIC review</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Supporting context only. Do not infer that this question diagnoses this blocker. UIC must validate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Draft - UIC review,Under UIC review,UIC approved,Rejected"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Direct,Contextual"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
